--- a/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
+++ b/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:05:07</t>
+          <t>02/08/2026 07:01:04</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:05:07</t>
+          <t>02/08/2026 07:01:04</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>04/07/2026 07:12:04</t>
+          <t>01/08/2026 07:04:04</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:02:05</t>
+          <t>01/08/2026 07:04:04</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:13:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:13:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>02/08/2026 07:00:04</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026 18:54:04</t>
+          <t>01/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:06:05</t>
+          <t>01/08/2026 07:07:04</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:06:05</t>
+          <t>01/08/2026 07:07:04</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:31:21</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:31:21</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:31:21</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:13:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P175" s="4" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P176" s="4" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>29/07/2026 07:19:34</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>29/07/2026 07:19:34</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>29/07/2026 07:19:34</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:13:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P202" s="4" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P203" s="4" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:08:04</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -16082,12 +16082,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="N209" s="5" t="n">
-        <v>100</v>
+      <c r="N209" s="6" t="n">
+        <v>66.188</v>
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:09:08</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P222" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="O223" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P223" s="4" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P224" s="4" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="O225" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P225" s="4" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P226" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="O227" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P227" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P228" s="4" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P229" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P230" s="4" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="O231" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P231" s="4" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P232" s="4" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O233" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P233" s="4" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P234" s="4" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P235" s="4" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P236" s="4" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P237" s="4" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P238" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P239" s="4" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P240" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P241" s="4" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P242" s="4" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P243" s="4" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P244" s="4" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P245" s="4" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P246" s="4" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P247" s="4" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P248" s="4" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P249" s="4" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P250" s="4" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P251" s="4" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P252" s="4" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P253" s="4" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P254" s="4" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P255" s="4" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P257" s="4" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P258" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P259" s="4" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P260" s="4" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P261" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P262" s="4" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P265" s="4" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P266" s="4" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P267" s="4" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P269" s="4" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P270" s="4" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P271" s="4" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O272" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P272" s="4" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O273" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P273" s="4" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="O275" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P275" s="4" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O277" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P277" s="4" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O279" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P279" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P281" s="4" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P282" s="4" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P283" s="4" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P284" s="4" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P285" s="4" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:48:18</t>
         </is>
       </c>
       <c r="P286" s="4" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P287" s="4" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P288" s="4" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P289" s="4" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P290" s="4" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P291" s="4" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P292" s="4" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P293" s="4" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P295" s="4" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P297" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P298" s="4" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P299" s="4" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P300" s="4" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P301" s="4" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P302" s="4" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P303" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P304" s="4" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P305" s="4" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P306" s="4" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P307" s="4" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P308" s="4" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P309" s="4" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P310" s="4" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P311" s="4" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P312" s="4" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P313" s="4" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P314" s="4" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P315" s="4" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P316" s="4" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P317" s="4" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P318" s="4" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P319" s="4" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P320" s="4" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P321" s="4" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P322" s="4" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P323" s="4" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P324" s="4" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P325" s="4" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P326" s="4" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:04:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P327" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P328" s="4" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P329" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P330" s="4" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P331" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P332" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P333" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P334" s="4" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P335" s="4" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P336" s="4" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P337" s="4" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P338" s="4" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P339" s="4" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P340" s="4" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>29/07/2026 07:47:09</t>
         </is>
       </c>
       <c r="P341" s="4" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P342" s="4" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P343" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P344" s="4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P345" s="4" t="inlineStr">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P346" s="4" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:06:04</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P348" s="4" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P349" s="4" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P350" s="4" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P351" s="4" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P352" s="4" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P353" s="4" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P354" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P355" s="4" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:36:08</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P356" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P357" s="4" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:00:04</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P358" s="4" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P359" s="4" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P360" s="4" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P361" s="4" t="inlineStr">
@@ -27715,7 +27715,7 @@
       </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P362" s="4" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P363" s="4" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P364" s="4" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P365" s="4" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P366" s="4" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P367" s="4" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P368" s="4" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>29/07/2026 07:14:22</t>
         </is>
       </c>
       <c r="P369" s="4" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P370" s="4" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P371" s="4" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P372" s="4" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P373" s="4" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P374" s="4" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P375" s="4" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P376" s="4" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P377" s="4" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P378" s="4" t="inlineStr">
@@ -29007,7 +29007,7 @@
       </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P379" s="4" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P380" s="4" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P381" s="4" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P382" s="4" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P383" s="4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P384" s="4" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:06:12</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P385" s="4" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:08:39</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P386" s="4" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P387" s="4" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P388" s="4" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P389" s="4" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P390" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P391" s="4" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:01:05</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P392" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P393" s="4" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P394" s="4" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P395" s="4" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P396" s="4" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
-          <t>21/07/2026 07:00:09</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P397" s="4" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P403" s="4" t="inlineStr">
@@ -30907,7 +30907,7 @@
       </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P404" s="4" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:01:07</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P405" s="4" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P406" s="4" t="inlineStr">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P407" s="4" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P408" s="4" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:02:06</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P409" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
       </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P410" s="4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:05:10</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P411" s="4" t="inlineStr">
@@ -32503,7 +32503,7 @@
       </c>
       <c r="O425" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:06:04</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P425" s="4" t="inlineStr">
@@ -32579,7 +32579,7 @@
       </c>
       <c r="O426" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:12:07</t>
+          <t>31/07/2026 20:56:07</t>
         </is>
       </c>
       <c r="P426" s="4" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>29/07/2026 07:03:31</t>
         </is>
       </c>
       <c r="P427" s="4" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P428" s="4" t="inlineStr">
@@ -32807,7 +32807,7 @@
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P429" s="4" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P430" s="4" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P431" s="4" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P432" s="4" t="inlineStr">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P433" s="4" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>29/07/2026 07:03:31</t>
         </is>
       </c>
       <c r="P434" s="4" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P435" s="4" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P436" s="4" t="inlineStr">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P437" s="4" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P438" s="4" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P439" s="4" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P440" s="4" t="inlineStr">
@@ -33719,7 +33719,7 @@
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P441" s="4" t="inlineStr">
@@ -33795,7 +33795,7 @@
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P442" s="4" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:00:12</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P443" s="4" t="inlineStr">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P444" s="4" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P445" s="4" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P446" s="4" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P447" s="4" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P448" s="4" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
-          <t>19/07/2026 07:00:14</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P449" s="4" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P450" s="4" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:43:16</t>
         </is>
       </c>
       <c r="P451" s="4" t="inlineStr">
@@ -34555,7 +34555,7 @@
       </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>29/07/2026 07:03:31</t>
         </is>
       </c>
       <c r="P452" s="4" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P453" s="4" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P454" s="4" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P455" s="4" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P456" s="4" t="inlineStr">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P457" s="4" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>29/07/2026 07:03:31</t>
         </is>
       </c>
       <c r="P458" s="4" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P459" s="4" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P460" s="4" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P461" s="4" t="inlineStr">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P462" s="4" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P463" s="4" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P464" s="4" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P465" s="4" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P466" s="4" t="inlineStr">
@@ -35695,7 +35695,7 @@
       </c>
       <c r="O467" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P467" s="4" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="O468" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P468" s="4" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P469" s="4" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P470" s="4" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P471" s="4" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:02:25</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P472" s="4" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P473" s="4" t="inlineStr">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P474" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026 07:00:11</t>
+          <t>31/07/2026 20:44:23</t>
         </is>
       </c>
       <c r="P475" s="4" t="inlineStr">
@@ -36531,7 +36531,7 @@
       </c>
       <c r="O478" s="4" t="inlineStr">
         <is>
-          <t>11/07/2026 07:11:11</t>
+          <t>25/07/2026 07:08:11</t>
         </is>
       </c>
       <c r="P478" s="4" t="inlineStr">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="O479" s="4" t="inlineStr">
         <is>
-          <t>11/07/2026 07:11:11</t>
+          <t>25/07/2026 07:08:11</t>
         </is>
       </c>
       <c r="P479" s="4" t="inlineStr">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="O482" s="4" t="inlineStr">
         <is>
-          <t>11/07/2026 07:11:11</t>
+          <t>25/07/2026 07:08:11</t>
         </is>
       </c>
       <c r="P482" s="4" t="inlineStr">
@@ -38127,7 +38127,7 @@
       </c>
       <c r="O499" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P499" s="4" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="O500" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P500" s="4" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P501" s="4" t="inlineStr">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="O504" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P504" s="4" t="inlineStr">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="O505" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P505" s="4" t="inlineStr">
@@ -38659,7 +38659,7 @@
       </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P506" s="4" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P507" s="4" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P508" s="4" t="inlineStr">
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P509" s="4" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="O510" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P510" s="4" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P511" s="4" t="inlineStr">
@@ -39115,7 +39115,7 @@
       </c>
       <c r="O512" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P512" s="4" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="O513" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P513" s="4" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="O514" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P514" s="4" t="inlineStr">
@@ -39571,7 +39571,7 @@
       </c>
       <c r="O518" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:27:06</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P518" s="4" t="inlineStr">
@@ -39647,7 +39647,7 @@
       </c>
       <c r="O519" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:27:06</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P519" s="4" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="O520" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:27:06</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P520" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:27:06</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr">
@@ -40027,7 +40027,7 @@
       </c>
       <c r="O524" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 07:01:04</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P524" s="4" t="inlineStr">
@@ -40331,7 +40331,7 @@
       </c>
       <c r="O528" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 07:01:04</t>
+          <t>31/07/2026 20:52:05</t>
         </is>
       </c>
       <c r="P528" s="4" t="inlineStr">
@@ -40787,7 +40787,7 @@
       </c>
       <c r="O534" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P534" s="4" t="inlineStr">
@@ -40863,7 +40863,7 @@
       </c>
       <c r="O535" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P535" s="4" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P536" s="4" t="inlineStr">
@@ -41015,7 +41015,7 @@
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P537" s="4" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P538" s="4" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P539" s="4" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P540" s="4" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:45:14</t>
+          <t>31/07/2026 21:00:31</t>
         </is>
       </c>
       <c r="P541" s="4" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P542" s="4" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P543" s="4" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P544" s="4" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P545" s="4" t="inlineStr">
@@ -41699,7 +41699,7 @@
       </c>
       <c r="O546" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P546" s="4" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P547" s="4" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P548" s="4" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="O552" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P552" s="4" t="inlineStr">
@@ -42231,7 +42231,7 @@
       </c>
       <c r="O553" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P553" s="4" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:13:09</t>
+          <t>31/07/2026 20:57:10</t>
         </is>
       </c>
       <c r="P554" s="4" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P555" s="4" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:45:57</t>
+          <t>31/07/2026 20:54:15</t>
         </is>
       </c>
       <c r="P556" s="4" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:32:20</t>
+          <t>29/07/2026 07:36:26</t>
         </is>
       </c>
       <c r="P557" s="4" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P558" s="4" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="O559" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:14:18</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P559" s="4" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
-          <t>08/07/2026 21:38:10</t>
+          <t>31/07/2026 20:49:23</t>
         </is>
       </c>
       <c r="P560" s="4" t="inlineStr">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:22:16</t>
+          <t>31/07/2026 20:50:24</t>
         </is>
       </c>
       <c r="P561" s="4" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:04:06</t>
+          <t>01/08/2026 07:06:06</t>
         </is>
       </c>
       <c r="P562" s="4" t="inlineStr">
@@ -42991,7 +42991,7 @@
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:04:06</t>
+          <t>01/08/2026 07:06:06</t>
         </is>
       </c>
       <c r="P563" s="4" t="inlineStr">
@@ -43067,7 +43067,7 @@
       </c>
       <c r="O564" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:04:06</t>
+          <t>01/08/2026 07:06:06</t>
         </is>
       </c>
       <c r="P564" s="4" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="O565" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P565" s="4" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="O566" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P566" s="4" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="O567" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P567" s="4" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="O568" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:38:41</t>
         </is>
       </c>
       <c r="P568" s="4" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="O569" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P569" s="4" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="O570" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P570" s="4" t="inlineStr">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="O571" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P571" s="4" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="O572" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P572" s="4" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O573" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P573" s="4" t="inlineStr">
@@ -43827,7 +43827,7 @@
       </c>
       <c r="O574" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P574" s="4" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:38:41</t>
         </is>
       </c>
       <c r="P575" s="4" t="inlineStr">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="O576" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P576" s="4" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="O577" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P577" s="4" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="O578" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P578" s="4" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="O579" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P579" s="4" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O580" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P580" s="4" t="inlineStr">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="O581" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P581" s="4" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="O582" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P582" s="4" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="O583" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P583" s="4" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="O584" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P584" s="4" t="inlineStr">
@@ -44663,7 +44663,7 @@
       </c>
       <c r="O585" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P585" s="4" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="O586" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P586" s="4" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="O587" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P587" s="4" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>31/07/2026 20:46:09</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:38:41</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
@@ -45271,7 +45271,7 @@
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
@@ -45423,7 +45423,7 @@
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="O600" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="O601" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:22:09</t>
         </is>
       </c>
       <c r="P601" s="4" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="O602" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="O603" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O604" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O605" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:25:15</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O606" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="O607" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P607" s="4" t="inlineStr">
@@ -46411,7 +46411,7 @@
       </c>
       <c r="O608" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:05:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P608" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="O609" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="O610" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="O611" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="O612" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="O613" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="O614" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:11:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="O615" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P615" s="4" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O616" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
@@ -47095,7 +47095,7 @@
       </c>
       <c r="O617" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="O618" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
@@ -47247,7 +47247,7 @@
       </c>
       <c r="O619" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:40:38</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="O620" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="O621" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="O622" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
@@ -47551,7 +47551,7 @@
       </c>
       <c r="O623" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:38:41</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="O624" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:11:06</t>
+          <t>29/07/2026 07:38:41</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
@@ -47703,7 +47703,7 @@
       </c>
       <c r="O625" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="O626" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="O627" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:41:32</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
@@ -47931,7 +47931,7 @@
       </c>
       <c r="O628" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="O629" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="O630" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
@@ -48159,7 +48159,7 @@
       </c>
       <c r="O631" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:41:32</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
@@ -48463,7 +48463,7 @@
       </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:23:39</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
@@ -48767,7 +48767,7 @@
       </c>
       <c r="O639" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:44:34</t>
         </is>
       </c>
       <c r="P639" s="4" t="inlineStr">
@@ -48843,7 +48843,7 @@
       </c>
       <c r="O640" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:44:34</t>
         </is>
       </c>
       <c r="P640" s="4" t="inlineStr">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>30/07/2026 07:02:41</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
@@ -49223,7 +49223,7 @@
       </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
@@ -49527,7 +49527,7 @@
       </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P650" s="4" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="O651" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P651" s="4" t="inlineStr">
@@ -49755,7 +49755,7 @@
       </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P652" s="4" t="inlineStr">
@@ -49831,7 +49831,7 @@
       </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P653" s="4" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P654" s="4" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P655" s="4" t="inlineStr">
@@ -50059,7 +50059,7 @@
       </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:25:15</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P656" s="4" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P657" s="4" t="inlineStr">
@@ -50211,7 +50211,7 @@
       </c>
       <c r="O658" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P658" s="4" t="inlineStr">
@@ -50287,7 +50287,7 @@
       </c>
       <c r="O659" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P659" s="4" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P660" s="4" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:05:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P661" s="4" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P662" s="4" t="inlineStr">
@@ -50591,7 +50591,7 @@
       </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P663" s="4" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P664" s="4" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P665" s="4" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P666" s="4" t="inlineStr">
@@ -50895,7 +50895,7 @@
       </c>
       <c r="O667" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P667" s="4" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="O668" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P668" s="4" t="inlineStr">
@@ -51047,7 +51047,7 @@
       </c>
       <c r="O669" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:11:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P669" s="4" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="O670" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P670" s="4" t="inlineStr">
@@ -51199,7 +51199,7 @@
       </c>
       <c r="O671" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P671" s="4" t="inlineStr">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="O672" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:45:36</t>
         </is>
       </c>
       <c r="P672" s="4" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="O673" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P673" s="4" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="O674" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:36:20</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P674" s="4" t="inlineStr">
@@ -51503,7 +51503,7 @@
       </c>
       <c r="O675" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:07:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P675" s="4" t="inlineStr">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="O676" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P676" s="4" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O677" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P677" s="4" t="inlineStr">
@@ -51731,7 +51731,7 @@
       </c>
       <c r="O678" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P678" s="4" t="inlineStr">
@@ -51807,7 +51807,7 @@
       </c>
       <c r="O679" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P679" s="4" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O680" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P680" s="4" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="O681" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P681" s="4" t="inlineStr">
@@ -52035,7 +52035,7 @@
       </c>
       <c r="O682" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>30/07/2026 07:02:41</t>
         </is>
       </c>
       <c r="P682" s="4" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O684" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P684" s="4" t="inlineStr">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="O685" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P685" s="4" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="O686" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P686" s="4" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="O687" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P687" s="4" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="O688" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P688" s="4" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P689" s="4" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="O690" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P690" s="4" t="inlineStr">
@@ -52719,7 +52719,7 @@
       </c>
       <c r="O691" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P691" s="4" t="inlineStr">
@@ -52795,7 +52795,7 @@
       </c>
       <c r="O692" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P692" s="4" t="inlineStr">
@@ -52871,7 +52871,7 @@
       </c>
       <c r="O693" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P693" s="4" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="O694" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P694" s="4" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="O695" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P695" s="4" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="O696" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P696" s="4" t="inlineStr">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="O697" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P697" s="4" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="O698" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P698" s="4" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="O699" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P699" s="4" t="inlineStr">
@@ -53403,7 +53403,7 @@
       </c>
       <c r="O700" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:07:42</t>
         </is>
       </c>
       <c r="P700" s="4" t="inlineStr">
@@ -53479,7 +53479,7 @@
       </c>
       <c r="O701" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P701" s="4" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="O702" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P702" s="4" t="inlineStr">
@@ -53631,7 +53631,7 @@
       </c>
       <c r="O703" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P703" s="4" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O704" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P704" s="4" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="O705" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P705" s="4" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O706" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P706" s="4" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="O707" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P707" s="4" t="inlineStr">
@@ -54011,7 +54011,7 @@
       </c>
       <c r="O708" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P708" s="4" t="inlineStr">
@@ -54087,7 +54087,7 @@
       </c>
       <c r="O709" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P709" s="4" t="inlineStr">
@@ -54163,7 +54163,7 @@
       </c>
       <c r="O710" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P710" s="4" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="O711" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P711" s="4" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="O712" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P712" s="4" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="O713" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P713" s="4" t="inlineStr">
@@ -54467,7 +54467,7 @@
       </c>
       <c r="O714" s="4" t="inlineStr">
         <is>
-          <t>14/07/2026 07:01:05</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P714" s="4" t="inlineStr">
@@ -54543,7 +54543,7 @@
       </c>
       <c r="O715" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P715" s="4" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="O716" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P716" s="4" t="inlineStr">
@@ -54695,7 +54695,7 @@
       </c>
       <c r="O717" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:05:48</t>
         </is>
       </c>
       <c r="P717" s="4" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="O718" s="4" t="inlineStr">
         <is>
-          <t>07/07/2026 07:05:21</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P718" s="4" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="O719" s="4" t="inlineStr">
         <is>
-          <t>16/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P719" s="4" t="inlineStr">
@@ -54923,7 +54923,7 @@
       </c>
       <c r="O720" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P720" s="4" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="O721" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:02:06</t>
+          <t>29/07/2026 07:09:36</t>
         </is>
       </c>
       <c r="P721" s="4" t="inlineStr">
@@ -55075,7 +55075,7 @@
       </c>
       <c r="O722" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P722" s="4" t="inlineStr">
@@ -55151,7 +55151,7 @@
       </c>
       <c r="O723" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P723" s="4" t="inlineStr">
@@ -55227,7 +55227,7 @@
       </c>
       <c r="O724" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P724" s="4" t="inlineStr">
@@ -55303,7 +55303,7 @@
       </c>
       <c r="O725" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P725" s="4" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="O726" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P726" s="4" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="O727" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P727" s="4" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="O728" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P728" s="4" t="inlineStr">
@@ -55607,7 +55607,7 @@
       </c>
       <c r="O729" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P729" s="4" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="O730" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P730" s="4" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="O731" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P731" s="4" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="O732" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P732" s="4" t="inlineStr">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="O733" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P733" s="4" t="inlineStr">
@@ -55987,7 +55987,7 @@
       </c>
       <c r="O734" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P734" s="4" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="O735" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P735" s="4" t="inlineStr">
@@ -56139,7 +56139,7 @@
       </c>
       <c r="O736" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P736" s="4" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="O737" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P737" s="4" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="O738" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P738" s="4" t="inlineStr">
@@ -56367,7 +56367,7 @@
       </c>
       <c r="O739" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:01:33</t>
+          <t>01/08/2026 07:03:12</t>
         </is>
       </c>
       <c r="P739" s="4" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="O740" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P740" s="4" t="inlineStr">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="O741" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P741" s="4" t="inlineStr">
@@ -56595,7 +56595,7 @@
       </c>
       <c r="O742" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P742" s="4" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="O743" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P743" s="4" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="O744" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:08:06</t>
+          <t>29/07/2026 07:46:38</t>
         </is>
       </c>
       <c r="P744" s="4" t="inlineStr">
@@ -56823,7 +56823,7 @@
       </c>
       <c r="O745" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P745" s="4" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="O746" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:04:06</t>
+          <t>29/07/2026 07:16:23</t>
         </is>
       </c>
       <c r="P746" s="4" t="inlineStr">
@@ -56975,7 +56975,7 @@
       </c>
       <c r="O747" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:06:05</t>
+          <t>29/07/2026 07:25:40</t>
         </is>
       </c>
       <c r="P747" s="4" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="O748" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:03:10</t>
+          <t>01/08/2026 07:05:08</t>
         </is>
       </c>
       <c r="P748" s="4" t="inlineStr">
@@ -57127,7 +57127,7 @@
       </c>
       <c r="O749" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:03:10</t>
+          <t>01/08/2026 07:05:08</t>
         </is>
       </c>
       <c r="P749" s="4" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="O750" s="4" t="inlineStr">
         <is>
-          <t>18/07/2026 07:03:10</t>
+          <t>01/08/2026 07:05:08</t>
         </is>
       </c>
       <c r="P750" s="4" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="O751" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P751" s="4" t="inlineStr">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="O752" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P752" s="4" t="inlineStr">
@@ -57431,7 +57431,7 @@
       </c>
       <c r="O753" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P753" s="4" t="inlineStr">
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O754" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P754" s="4" t="inlineStr">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O755" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P755" s="4" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="O756" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P756" s="4" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="O757" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P757" s="4" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="O758" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P758" s="4" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="O759" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P759" s="4" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="O760" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P760" s="4" t="inlineStr">
@@ -58039,7 +58039,7 @@
       </c>
       <c r="O761" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P761" s="4" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="O762" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026 07:07:04</t>
+          <t>29/07/2026 07:37:08</t>
         </is>
       </c>
       <c r="P762" s="4" t="inlineStr">
@@ -58252,7 +58252,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>4608033</v>
+        <v>4608086</v>
       </c>
     </row>
     <row r="8">
@@ -58417,7 +58417,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
+++ b/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
@@ -713,29 +713,29 @@
         <v>1</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>4.2893</v>
+        <v>9.975</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>02/08/2026 07:01:04</t>
+          <t>06/08/2026 07:37:36</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>02/08/2026 07:01:04</t>
+          <t>07/08/2026 17:29:13</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>07/08/2026 17:22:45</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:49:44</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>08/08/2026 07:00:31</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>02/08/2026 07:00:04</t>
+          <t>07/08/2026 17:24:49</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:07:04</t>
+          <t>07/08/2026 17:30:06</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>05/08/2026 07:04:04</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:07:04</t>
+          <t>07/08/2026 17:30:06</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>05/08/2026 07:04:04</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>05/08/2026 07:01:04</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>05/08/2026 07:00:27</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>04/08/2026 09:45:43</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P175" s="4" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P176" s="4" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:19:34</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:19:34</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P202" s="4" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P203" s="4" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P222" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="O223" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:13:25</t>
         </is>
       </c>
       <c r="P223" s="4" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P224" s="4" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="O225" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P225" s="4" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P226" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="O227" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P227" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P228" s="4" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P229" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P230" s="4" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="O231" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P231" s="4" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P232" s="4" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O233" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P233" s="4" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P234" s="4" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P235" s="4" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P236" s="4" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P237" s="4" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P238" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P239" s="4" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P240" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P241" s="4" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P242" s="4" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P243" s="4" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P244" s="4" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P245" s="4" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P246" s="4" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P247" s="4" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P248" s="4" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>06/08/2026 18:37:22</t>
         </is>
       </c>
       <c r="P249" s="4" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>06/08/2026 18:37:22</t>
         </is>
       </c>
       <c r="P250" s="4" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P251" s="4" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P252" s="4" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P253" s="4" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P254" s="4" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P255" s="4" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P257" s="4" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P258" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P259" s="4" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:37:36</t>
         </is>
       </c>
       <c r="P260" s="4" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P261" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P262" s="4" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P265" s="4" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:05:27</t>
         </is>
       </c>
       <c r="P266" s="4" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P267" s="4" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P269" s="4" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P270" s="4" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P271" s="4" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O272" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P272" s="4" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O273" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P273" s="4" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="O275" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P275" s="4" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O277" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P277" s="4" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O279" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P279" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P281" s="4" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P282" s="4" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:14:25</t>
         </is>
       </c>
       <c r="P283" s="4" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P284" s="4" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P285" s="4" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:48:18</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P286" s="4" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P287" s="4" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P288" s="4" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P289" s="4" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P290" s="4" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P291" s="4" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P292" s="4" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P293" s="4" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P295" s="4" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P297" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P298" s="4" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P299" s="4" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P300" s="4" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P301" s="4" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P302" s="4" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P303" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P304" s="4" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P305" s="4" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P306" s="4" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P307" s="4" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P308" s="4" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>06/08/2026 18:37:22</t>
         </is>
       </c>
       <c r="P309" s="4" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>06/08/2026 18:37:22</t>
         </is>
       </c>
       <c r="P310" s="4" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P311" s="4" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P312" s="4" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P313" s="4" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P314" s="4" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P315" s="4" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P316" s="4" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P317" s="4" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P318" s="4" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P319" s="4" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P320" s="4" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P321" s="4" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P322" s="4" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P323" s="4" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P324" s="4" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P325" s="4" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P326" s="4" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P327" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P328" s="4" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P329" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P330" s="4" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P331" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P332" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P333" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P334" s="4" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P335" s="4" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P336" s="4" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P337" s="4" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P338" s="4" t="inlineStr">
@@ -25963,11 +25963,11 @@
         </is>
       </c>
       <c r="N339" s="6" t="n">
-        <v>26.291</v>
+        <v>12.687</v>
       </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P339" s="4" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P340" s="4" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:47:09</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P341" s="4" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P342" s="4" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P343" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P344" s="4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P345" s="4" t="inlineStr">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>04/08/2026 11:40:41</t>
         </is>
       </c>
       <c r="P346" s="4" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P348" s="4" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P349" s="4" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P350" s="4" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P351" s="4" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P352" s="4" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P353" s="4" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P354" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P355" s="4" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P356" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P357" s="4" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P358" s="4" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P359" s="4" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P360" s="4" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P361" s="4" t="inlineStr">
@@ -27715,7 +27715,7 @@
       </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P362" s="4" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:15:23</t>
         </is>
       </c>
       <c r="P363" s="4" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P364" s="4" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P365" s="4" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P366" s="4" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P367" s="4" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P368" s="4" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:14:22</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P369" s="4" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>06/08/2026 18:37:22</t>
         </is>
       </c>
       <c r="P370" s="4" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P371" s="4" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P372" s="4" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P373" s="4" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P374" s="4" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P375" s="4" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P376" s="4" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P377" s="4" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P378" s="4" t="inlineStr">
@@ -29007,7 +29007,7 @@
       </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P379" s="4" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P380" s="4" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P381" s="4" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P382" s="4" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>06/08/2026 18:25:49</t>
         </is>
       </c>
       <c r="P383" s="4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P384" s="4" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P385" s="4" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P386" s="4" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P387" s="4" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P388" s="4" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P389" s="4" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P390" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P391" s="4" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P392" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P393" s="4" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P394" s="4" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P395" s="4" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>06/08/2026 18:42:20</t>
         </is>
       </c>
       <c r="P396" s="4" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P397" s="4" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P403" s="4" t="inlineStr">
@@ -30907,7 +30907,7 @@
       </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P404" s="4" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P405" s="4" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P406" s="4" t="inlineStr">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P407" s="4" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P408" s="4" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P409" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
       </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P410" s="4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P411" s="4" t="inlineStr">
@@ -32503,7 +32503,7 @@
       </c>
       <c r="O425" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P425" s="4" t="inlineStr">
@@ -32579,7 +32579,7 @@
       </c>
       <c r="O426" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:56:07</t>
+          <t>07/08/2026 07:23:06</t>
         </is>
       </c>
       <c r="P426" s="4" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:03:31</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P427" s="4" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P428" s="4" t="inlineStr">
@@ -32807,7 +32807,7 @@
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P429" s="4" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P430" s="4" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P431" s="4" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P432" s="4" t="inlineStr">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P433" s="4" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:03:31</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P434" s="4" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P435" s="4" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P436" s="4" t="inlineStr">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P437" s="4" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P438" s="4" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P439" s="4" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P440" s="4" t="inlineStr">
@@ -33719,7 +33719,7 @@
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P441" s="4" t="inlineStr">
@@ -33795,7 +33795,7 @@
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P442" s="4" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P443" s="4" t="inlineStr">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P444" s="4" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P445" s="4" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P446" s="4" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P447" s="4" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P448" s="4" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P449" s="4" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P450" s="4" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:43:16</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P451" s="4" t="inlineStr">
@@ -34555,7 +34555,7 @@
       </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:03:31</t>
+          <t>07/08/2026 07:00:47</t>
         </is>
       </c>
       <c r="P452" s="4" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P453" s="4" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P454" s="4" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P455" s="4" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P456" s="4" t="inlineStr">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P457" s="4" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:03:31</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P458" s="4" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P459" s="4" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P460" s="4" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P461" s="4" t="inlineStr">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P462" s="4" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P463" s="4" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P464" s="4" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P465" s="4" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P466" s="4" t="inlineStr">
@@ -35695,7 +35695,7 @@
       </c>
       <c r="O467" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P467" s="4" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="O468" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P468" s="4" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P469" s="4" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P470" s="4" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P471" s="4" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P472" s="4" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P473" s="4" t="inlineStr">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>04/08/2026 09:47:40</t>
         </is>
       </c>
       <c r="P474" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:44:23</t>
+          <t>07/08/2026 07:02:39</t>
         </is>
       </c>
       <c r="P475" s="4" t="inlineStr">
@@ -38127,7 +38127,7 @@
       </c>
       <c r="O499" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P499" s="4" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="O500" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P500" s="4" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P501" s="4" t="inlineStr">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="O504" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P504" s="4" t="inlineStr">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="O505" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P505" s="4" t="inlineStr">
@@ -38659,7 +38659,7 @@
       </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P506" s="4" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P507" s="4" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P508" s="4" t="inlineStr">
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P509" s="4" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P511" s="4" t="inlineStr">
@@ -39115,7 +39115,7 @@
       </c>
       <c r="O512" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P512" s="4" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="O513" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P513" s="4" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="O514" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P514" s="4" t="inlineStr">
@@ -39571,7 +39571,7 @@
       </c>
       <c r="O518" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>07/08/2026 07:11:05</t>
         </is>
       </c>
       <c r="P518" s="4" t="inlineStr">
@@ -39647,7 +39647,7 @@
       </c>
       <c r="O519" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>04/08/2026 10:45:05</t>
         </is>
       </c>
       <c r="P519" s="4" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="O520" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>07/08/2026 07:11:05</t>
         </is>
       </c>
       <c r="P520" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>07/08/2026 07:11:05</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr">
@@ -40027,7 +40027,7 @@
       </c>
       <c r="O524" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>07/08/2026 07:11:05</t>
         </is>
       </c>
       <c r="P524" s="4" t="inlineStr">
@@ -40331,7 +40331,7 @@
       </c>
       <c r="O528" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:52:05</t>
+          <t>07/08/2026 07:11:05</t>
         </is>
       </c>
       <c r="P528" s="4" t="inlineStr">
@@ -40787,7 +40787,7 @@
       </c>
       <c r="O534" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P534" s="4" t="inlineStr">
@@ -40863,7 +40863,7 @@
       </c>
       <c r="O535" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P535" s="4" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P536" s="4" t="inlineStr">
@@ -41015,7 +41015,7 @@
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P537" s="4" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P538" s="4" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P539" s="4" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P540" s="4" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 21:00:31</t>
+          <t>07/08/2026 07:28:10</t>
         </is>
       </c>
       <c r="P541" s="4" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P542" s="4" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P543" s="4" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P544" s="4" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P545" s="4" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P547" s="4" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P548" s="4" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="O552" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P552" s="4" t="inlineStr">
@@ -42231,7 +42231,7 @@
       </c>
       <c r="O553" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P553" s="4" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:57:10</t>
+          <t>07/08/2026 07:24:15</t>
         </is>
       </c>
       <c r="P554" s="4" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P555" s="4" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:54:15</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P556" s="4" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:36:26</t>
+          <t>07/08/2026 07:16:22</t>
         </is>
       </c>
       <c r="P557" s="4" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P558" s="4" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:49:23</t>
+          <t>07/08/2026 07:06:27</t>
         </is>
       </c>
       <c r="P560" s="4" t="inlineStr">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:50:24</t>
+          <t>04/08/2026 10:38:32</t>
         </is>
       </c>
       <c r="P561" s="4" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:06:06</t>
+          <t>08/08/2026 07:08:04</t>
         </is>
       </c>
       <c r="P562" s="4" t="inlineStr">
@@ -42991,7 +42991,7 @@
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:06:06</t>
+          <t>08/08/2026 07:08:04</t>
         </is>
       </c>
       <c r="P563" s="4" t="inlineStr">
@@ -43067,7 +43067,7 @@
       </c>
       <c r="O564" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:06:06</t>
+          <t>08/08/2026 07:08:04</t>
         </is>
       </c>
       <c r="P564" s="4" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="O565" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P565" s="4" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="O566" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P566" s="4" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="O567" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P567" s="4" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="O568" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:38:41</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P568" s="4" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="O569" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P569" s="4" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="O570" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P570" s="4" t="inlineStr">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="O571" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P571" s="4" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="O572" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P572" s="4" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O573" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P573" s="4" t="inlineStr">
@@ -43827,7 +43827,7 @@
       </c>
       <c r="O574" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P574" s="4" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:38:41</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P575" s="4" t="inlineStr">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="O576" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P576" s="4" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="O577" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P577" s="4" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="O578" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P578" s="4" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="O579" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P579" s="4" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O580" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P580" s="4" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="O582" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P582" s="4" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="O583" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P583" s="4" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="O584" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P584" s="4" t="inlineStr">
@@ -44663,7 +44663,7 @@
       </c>
       <c r="O585" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P585" s="4" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="O586" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P586" s="4" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
-          <t>31/07/2026 20:46:09</t>
+          <t>04/08/2026 10:24:41</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:38:41</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
@@ -45271,7 +45271,7 @@
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
@@ -45423,7 +45423,7 @@
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="O600" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="O601" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:22:09</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P601" s="4" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="O602" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="O603" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O604" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O605" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O606" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="O607" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P607" s="4" t="inlineStr">
@@ -46411,7 +46411,7 @@
       </c>
       <c r="O608" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P608" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="O609" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="O610" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="O611" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="O612" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="O613" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="O614" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="O615" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P615" s="4" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O616" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
@@ -47095,7 +47095,7 @@
       </c>
       <c r="O617" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="O618" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
@@ -47247,7 +47247,7 @@
       </c>
       <c r="O619" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:40:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="O620" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="O621" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="O622" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
@@ -47551,7 +47551,7 @@
       </c>
       <c r="O623" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:38:41</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="O624" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:38:41</t>
+          <t>07/08/2026 07:19:34</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
@@ -47703,7 +47703,7 @@
       </c>
       <c r="O625" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:07:30</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="O626" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="O627" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:41:32</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
@@ -47931,7 +47931,7 @@
       </c>
       <c r="O628" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="O629" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:08:33</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="O630" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
@@ -48159,7 +48159,7 @@
       </c>
       <c r="O631" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:08:33</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:41:32</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
@@ -48463,7 +48463,7 @@
       </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:08:33</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:23:39</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
@@ -48767,7 +48767,7 @@
       </c>
       <c r="O639" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:44:34</t>
+          <t>07/08/2026 07:21:30</t>
         </is>
       </c>
       <c r="P639" s="4" t="inlineStr">
@@ -48843,7 +48843,7 @@
       </c>
       <c r="O640" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:44:34</t>
+          <t>07/08/2026 07:21:30</t>
         </is>
       </c>
       <c r="P640" s="4" t="inlineStr">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:21:30</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
-          <t>30/07/2026 07:02:41</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
@@ -49223,7 +49223,7 @@
       </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
@@ -49527,7 +49527,7 @@
       </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P650" s="4" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="O651" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P651" s="4" t="inlineStr">
@@ -49755,7 +49755,7 @@
       </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P652" s="4" t="inlineStr">
@@ -49831,7 +49831,7 @@
       </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P653" s="4" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P654" s="4" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P655" s="4" t="inlineStr">
@@ -50059,7 +50059,7 @@
       </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P656" s="4" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P657" s="4" t="inlineStr">
@@ -50211,7 +50211,7 @@
       </c>
       <c r="O658" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P658" s="4" t="inlineStr">
@@ -50287,7 +50287,7 @@
       </c>
       <c r="O659" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P659" s="4" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P660" s="4" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P661" s="4" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P662" s="4" t="inlineStr">
@@ -50591,7 +50591,7 @@
       </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P663" s="4" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P664" s="4" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P665" s="4" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P666" s="4" t="inlineStr">
@@ -50895,7 +50895,7 @@
       </c>
       <c r="O667" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P667" s="4" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="O668" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P668" s="4" t="inlineStr">
@@ -51047,7 +51047,7 @@
       </c>
       <c r="O669" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P669" s="4" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="O670" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P670" s="4" t="inlineStr">
@@ -51199,7 +51199,7 @@
       </c>
       <c r="O671" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P671" s="4" t="inlineStr">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="O672" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:45:36</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P672" s="4" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="O673" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P673" s="4" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="O674" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P674" s="4" t="inlineStr">
@@ -51503,7 +51503,7 @@
       </c>
       <c r="O675" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P675" s="4" t="inlineStr">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="O676" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P676" s="4" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O677" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P677" s="4" t="inlineStr">
@@ -51731,7 +51731,7 @@
       </c>
       <c r="O678" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P678" s="4" t="inlineStr">
@@ -51807,7 +51807,7 @@
       </c>
       <c r="O679" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P679" s="4" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O680" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P680" s="4" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="O681" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P681" s="4" t="inlineStr">
@@ -52035,7 +52035,7 @@
       </c>
       <c r="O682" s="4" t="inlineStr">
         <is>
-          <t>30/07/2026 07:02:41</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P682" s="4" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O684" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P684" s="4" t="inlineStr">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="O685" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P685" s="4" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="O686" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P686" s="4" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="O687" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P687" s="4" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="O688" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P688" s="4" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>08/08/2026 07:02:04</t>
         </is>
       </c>
       <c r="P689" s="4" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="O690" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P690" s="4" t="inlineStr">
@@ -52719,7 +52719,7 @@
       </c>
       <c r="O691" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P691" s="4" t="inlineStr">
@@ -52795,7 +52795,7 @@
       </c>
       <c r="O692" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P692" s="4" t="inlineStr">
@@ -52871,7 +52871,7 @@
       </c>
       <c r="O693" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P693" s="4" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="O694" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P694" s="4" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="O695" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P695" s="4" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="O696" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P696" s="4" t="inlineStr">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="O697" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P697" s="4" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="O698" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P698" s="4" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="O699" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P699" s="4" t="inlineStr">
@@ -53403,7 +53403,7 @@
       </c>
       <c r="O700" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:07:42</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P700" s="4" t="inlineStr">
@@ -53479,7 +53479,7 @@
       </c>
       <c r="O701" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P701" s="4" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="O702" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P702" s="4" t="inlineStr">
@@ -53631,7 +53631,7 @@
       </c>
       <c r="O703" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P703" s="4" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O704" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P704" s="4" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="O705" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P705" s="4" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O706" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P706" s="4" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="O707" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P707" s="4" t="inlineStr">
@@ -54011,7 +54011,7 @@
       </c>
       <c r="O708" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P708" s="4" t="inlineStr">
@@ -54087,7 +54087,7 @@
       </c>
       <c r="O709" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P709" s="4" t="inlineStr">
@@ -54163,7 +54163,7 @@
       </c>
       <c r="O710" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P710" s="4" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="O711" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P711" s="4" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="O712" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P712" s="4" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="O713" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P713" s="4" t="inlineStr">
@@ -54467,7 +54467,7 @@
       </c>
       <c r="O714" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P714" s="4" t="inlineStr">
@@ -54543,7 +54543,7 @@
       </c>
       <c r="O715" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P715" s="4" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="O716" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P716" s="4" t="inlineStr">
@@ -54695,7 +54695,7 @@
       </c>
       <c r="O717" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:05:48</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P717" s="4" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="O718" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P718" s="4" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="O719" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P719" s="4" t="inlineStr">
@@ -54923,7 +54923,7 @@
       </c>
       <c r="O720" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>06/08/2026 18:27:06</t>
         </is>
       </c>
       <c r="P720" s="4" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="O721" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:09:36</t>
+          <t>07/08/2026 07:04:30</t>
         </is>
       </c>
       <c r="P721" s="4" t="inlineStr">
@@ -55075,7 +55075,7 @@
       </c>
       <c r="O722" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P722" s="4" t="inlineStr">
@@ -55151,7 +55151,7 @@
       </c>
       <c r="O723" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P723" s="4" t="inlineStr">
@@ -55227,7 +55227,7 @@
       </c>
       <c r="O724" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P724" s="4" t="inlineStr">
@@ -55303,7 +55303,7 @@
       </c>
       <c r="O725" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P725" s="4" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="O726" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P726" s="4" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="O727" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P727" s="4" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="O728" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P728" s="4" t="inlineStr">
@@ -55607,7 +55607,7 @@
       </c>
       <c r="O729" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P729" s="4" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="O730" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P730" s="4" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="O731" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P731" s="4" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="O732" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P732" s="4" t="inlineStr">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="O733" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P733" s="4" t="inlineStr">
@@ -55987,7 +55987,7 @@
       </c>
       <c r="O734" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P734" s="4" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="O735" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P735" s="4" t="inlineStr">
@@ -56139,7 +56139,7 @@
       </c>
       <c r="O736" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P736" s="4" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="O737" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P737" s="4" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="O738" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P738" s="4" t="inlineStr">
@@ -56367,7 +56367,7 @@
       </c>
       <c r="O739" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:03:12</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P739" s="4" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="O740" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P740" s="4" t="inlineStr">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="O741" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P741" s="4" t="inlineStr">
@@ -56595,7 +56595,7 @@
       </c>
       <c r="O742" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P742" s="4" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="O743" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>08/08/2026 07:06:17</t>
         </is>
       </c>
       <c r="P743" s="4" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="O744" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:46:38</t>
+          <t>07/08/2026 07:22:32</t>
         </is>
       </c>
       <c r="P744" s="4" t="inlineStr">
@@ -56823,7 +56823,7 @@
       </c>
       <c r="O745" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>06/08/2026 18:38:08</t>
         </is>
       </c>
       <c r="P745" s="4" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="O746" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:16:23</t>
+          <t>07/08/2026 07:10:28</t>
         </is>
       </c>
       <c r="P746" s="4" t="inlineStr">
@@ -56975,7 +56975,7 @@
       </c>
       <c r="O747" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:25:40</t>
+          <t>06/08/2026 18:43:06</t>
         </is>
       </c>
       <c r="P747" s="4" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="O748" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:05:08</t>
+          <t>08/08/2026 07:07:04</t>
         </is>
       </c>
       <c r="P748" s="4" t="inlineStr">
@@ -57127,7 +57127,7 @@
       </c>
       <c r="O749" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:05:08</t>
+          <t>08/08/2026 07:07:04</t>
         </is>
       </c>
       <c r="P749" s="4" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="O750" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:05:08</t>
+          <t>08/08/2026 07:07:04</t>
         </is>
       </c>
       <c r="P750" s="4" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="O751" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P751" s="4" t="inlineStr">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="O752" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P752" s="4" t="inlineStr">
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O754" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P754" s="4" t="inlineStr">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O755" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P755" s="4" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="O756" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P756" s="4" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="O757" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P757" s="4" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="O758" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P758" s="4" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="O759" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P759" s="4" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="O760" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P760" s="4" t="inlineStr">
@@ -58039,7 +58039,7 @@
       </c>
       <c r="O761" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P761" s="4" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="O762" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>08/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P762" s="4" t="inlineStr">
@@ -58229,7 +58229,7 @@
         <v>555</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>685557</v>
+        <v>685582</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>4608086</v>
+        <v>4608054</v>
       </c>
     </row>
     <row r="8">
@@ -58293,7 +58293,7 @@
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2732699</v>
+        <v>2732612</v>
       </c>
     </row>
     <row r="9">
@@ -58417,7 +58417,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -58472,7 +58472,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1088851</v>
+        <v>1088876</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
+++ b/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
@@ -2635,7 +2635,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:04:04</t>
+          <t>23/08/2026 07:14:05</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:04:04</t>
+          <t>23/08/2026 07:14:05</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:58:32</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:00:06</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:58:32</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:58:32</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>21/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:58:32</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:04:04</t>
+          <t>21/08/2026 07:06:03</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:16:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:04:04</t>
+          <t>21/08/2026 07:06:03</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:16:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:20:28</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:58:32</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:20:28</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:20:28</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:03:04</t>
+          <t>23/08/2026 07:10:04</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:54:14</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:09:30</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P222" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="O223" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P223" s="4" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P224" s="4" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="O225" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P225" s="4" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P226" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="O227" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P227" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P228" s="4" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P229" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P230" s="4" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="O231" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P231" s="4" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P232" s="4" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O233" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P233" s="4" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P234" s="4" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P235" s="4" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P236" s="4" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P237" s="4" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P238" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P239" s="4" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P240" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P241" s="4" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P242" s="4" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P243" s="4" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P244" s="4" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P245" s="4" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P246" s="4" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P247" s="4" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P248" s="4" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P249" s="4" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P250" s="4" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P251" s="4" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P252" s="4" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P253" s="4" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P254" s="4" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:04:05</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P255" s="4" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:04:05</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P257" s="4" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P258" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P259" s="4" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P260" s="4" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P261" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P262" s="4" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P265" s="4" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P266" s="4" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P267" s="4" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P269" s="4" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P270" s="4" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:21:34</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P271" s="4" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O272" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P272" s="4" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O273" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P273" s="4" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="O275" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P275" s="4" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O277" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P277" s="4" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O279" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P279" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P281" s="4" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P282" s="4" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P283" s="4" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P284" s="4" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P285" s="4" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P286" s="4" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P287" s="4" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P288" s="4" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P289" s="4" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P290" s="4" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P291" s="4" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P292" s="4" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P293" s="4" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P295" s="4" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P297" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P298" s="4" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P299" s="4" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P300" s="4" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P301" s="4" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P302" s="4" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P303" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P304" s="4" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P305" s="4" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P306" s="4" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P307" s="4" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P308" s="4" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P309" s="4" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P310" s="4" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P311" s="4" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P312" s="4" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P313" s="4" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P314" s="4" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P315" s="4" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P316" s="4" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P317" s="4" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P318" s="4" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P319" s="4" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P320" s="4" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P321" s="4" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P322" s="4" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P323" s="4" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P324" s="4" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P325" s="4" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P326" s="4" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P327" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P328" s="4" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P329" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P330" s="4" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P331" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P332" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P333" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P334" s="4" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P335" s="4" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P336" s="4" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P337" s="4" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P338" s="4" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P339" s="4" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P340" s="4" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P341" s="4" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:16:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P342" s="4" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:41:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P343" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:16:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P344" s="4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:41:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P345" s="4" t="inlineStr">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P346" s="4" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:16:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P348" s="4" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P349" s="4" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P350" s="4" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P351" s="4" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P352" s="4" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P353" s="4" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P354" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P355" s="4" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P356" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P357" s="4" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P358" s="4" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P359" s="4" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P360" s="4" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P361" s="4" t="inlineStr">
@@ -27715,7 +27715,7 @@
       </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P362" s="4" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P363" s="4" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P364" s="4" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P365" s="4" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P366" s="4" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P367" s="4" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P368" s="4" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P369" s="4" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P370" s="4" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:35:08</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P371" s="4" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P372" s="4" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P373" s="4" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P374" s="4" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P375" s="4" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P376" s="4" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P377" s="4" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P378" s="4" t="inlineStr">
@@ -29007,7 +29007,7 @@
       </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P379" s="4" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P380" s="4" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P381" s="4" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P382" s="4" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P383" s="4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P384" s="4" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P385" s="4" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P386" s="4" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P387" s="4" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:23:41</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P388" s="4" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P389" s="4" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P390" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P391" s="4" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P392" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P393" s="4" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P394" s="4" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P395" s="4" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P396" s="4" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P397" s="4" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="O398" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P398" s="4" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="O399" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P399" s="4" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:40:13</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P405" s="4" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P406" s="4" t="inlineStr">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P407" s="4" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P408" s="4" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:23:41</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P409" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
       </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P410" s="4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P411" s="4" t="inlineStr">
@@ -31515,7 +31515,7 @@
       </c>
       <c r="O412" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P412" s="4" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="O413" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P413" s="4" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P427" s="4" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:42:05</t>
+          <t>20/08/2026 07:06:05</t>
         </is>
       </c>
       <c r="P428" s="4" t="inlineStr">
@@ -32807,7 +32807,7 @@
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P429" s="4" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P430" s="4" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P431" s="4" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P432" s="4" t="inlineStr">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P433" s="4" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P434" s="4" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P435" s="4" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:33:09</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P436" s="4" t="inlineStr">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P437" s="4" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P438" s="4" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P439" s="4" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P440" s="4" t="inlineStr">
@@ -33719,7 +33719,7 @@
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P441" s="4" t="inlineStr">
@@ -33795,7 +33795,7 @@
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P442" s="4" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P443" s="4" t="inlineStr">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P444" s="4" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P445" s="4" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P446" s="4" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P447" s="4" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P448" s="4" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P449" s="4" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P450" s="4" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P451" s="4" t="inlineStr">
@@ -34555,7 +34555,7 @@
       </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P452" s="4" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P453" s="4" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P454" s="4" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P455" s="4" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P456" s="4" t="inlineStr">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P457" s="4" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P458" s="4" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P459" s="4" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:33:09</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P460" s="4" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P461" s="4" t="inlineStr">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P462" s="4" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P463" s="4" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P464" s="4" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:00:12</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P465" s="4" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P466" s="4" t="inlineStr">
@@ -35695,7 +35695,7 @@
       </c>
       <c r="O467" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P467" s="4" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="O468" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P468" s="4" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P469" s="4" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P470" s="4" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P471" s="4" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P472" s="4" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P473" s="4" t="inlineStr">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P474" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P475" s="4" t="inlineStr">
@@ -36379,7 +36379,7 @@
       </c>
       <c r="O476" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:59:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P476" s="4" t="inlineStr">
@@ -36455,7 +36455,7 @@
       </c>
       <c r="O477" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:00:27</t>
+          <t>20/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P477" s="4" t="inlineStr">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="O480" s="4" t="inlineStr">
         <is>
-          <t>25/07/2026 07:08:11</t>
+          <t>23/08/2026 07:13:04</t>
         </is>
       </c>
       <c r="P480" s="4" t="inlineStr">
@@ -36759,7 +36759,7 @@
       </c>
       <c r="O481" s="4" t="inlineStr">
         <is>
-          <t>25/07/2026 07:08:11</t>
+          <t>23/08/2026 07:13:04</t>
         </is>
       </c>
       <c r="P481" s="4" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P501" s="4" t="inlineStr">
@@ -38355,7 +38355,7 @@
       </c>
       <c r="O502" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P502" s="4" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O503" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P503" s="4" t="inlineStr">
@@ -38659,7 +38659,7 @@
       </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P506" s="4" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P507" s="4" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P508" s="4" t="inlineStr">
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P509" s="4" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="O510" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P510" s="4" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P511" s="4" t="inlineStr">
@@ -39115,7 +39115,7 @@
       </c>
       <c r="O512" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P512" s="4" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="O513" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P513" s="4" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="O514" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P514" s="4" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="O515" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P515" s="4" t="inlineStr">
@@ -39419,7 +39419,7 @@
       </c>
       <c r="O516" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P516" s="4" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="O520" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:05:04</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P520" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:05:04</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="O522" s="4" t="inlineStr">
         <is>
-          <t>16/08/2026 07:01:05</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P522" s="4" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="O523" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:05:04</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P523" s="4" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="O526" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 08:38:04</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P526" s="4" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="O530" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:17:04</t>
+          <t>20/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P530" s="4" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P536" s="4" t="inlineStr">
@@ -41015,7 +41015,7 @@
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P537" s="4" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P538" s="4" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:19:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P539" s="4" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P540" s="4" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:15:06</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P541" s="4" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P542" s="4" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:53:05</t>
+          <t>20/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P543" s="4" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P544" s="4" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P545" s="4" t="inlineStr">
@@ -41699,7 +41699,7 @@
       </c>
       <c r="O546" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P546" s="4" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P547" s="4" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P548" s="4" t="inlineStr">
@@ -41927,7 +41927,7 @@
       </c>
       <c r="O549" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P549" s="4" t="inlineStr">
@@ -42003,7 +42003,7 @@
       </c>
       <c r="O550" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P550" s="4" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P554" s="4" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:02:14</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P555" s="4" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:17:08</t>
+          <t>20/08/2026 07:07:05</t>
         </is>
       </c>
       <c r="P556" s="4" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P557" s="4" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:07:20</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P558" s="4" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="O559" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:08:19</t>
+          <t>20/08/2026 07:05:14</t>
         </is>
       </c>
       <c r="P559" s="4" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:03:09</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P560" s="4" t="inlineStr">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:05:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P561" s="4" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:02:19</t>
+          <t>20/08/2026 07:01:14</t>
         </is>
       </c>
       <c r="P562" s="4" t="inlineStr">
@@ -42991,7 +42991,7 @@
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:10:24</t>
+          <t>20/08/2026 07:02:08</t>
         </is>
       </c>
       <c r="P563" s="4" t="inlineStr">
@@ -43067,7 +43067,7 @@
       </c>
       <c r="O564" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:15:04</t>
+          <t>23/08/2026 07:16:06</t>
         </is>
       </c>
       <c r="P564" s="4" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="O565" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:15:04</t>
+          <t>23/08/2026 07:16:06</t>
         </is>
       </c>
       <c r="P565" s="4" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="O566" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:15:04</t>
+          <t>23/08/2026 07:16:06</t>
         </is>
       </c>
       <c r="P566" s="4" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="O567" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>19/08/2026 07:11:18</t>
         </is>
       </c>
       <c r="P567" s="4" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="O568" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P568" s="4" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="O569" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P569" s="4" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="O570" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P570" s="4" t="inlineStr">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="O571" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P571" s="4" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="O572" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P572" s="4" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O573" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P573" s="4" t="inlineStr">
@@ -43827,7 +43827,7 @@
       </c>
       <c r="O574" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P574" s="4" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P575" s="4" t="inlineStr">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="O576" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P576" s="4" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="O577" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P577" s="4" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="O578" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P578" s="4" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="O579" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P579" s="4" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O580" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P580" s="4" t="inlineStr">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="O581" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P581" s="4" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="O582" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P582" s="4" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="O583" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P583" s="4" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="O584" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P584" s="4" t="inlineStr">
@@ -44663,7 +44663,7 @@
       </c>
       <c r="O585" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P585" s="4" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="O586" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P586" s="4" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="O587" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P587" s="4" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
@@ -45271,7 +45271,7 @@
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
@@ -45423,7 +45423,7 @@
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="O600" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="O602" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="O603" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O604" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O605" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O606" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="O609" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="O610" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="O611" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="O612" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="O613" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="O614" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O616" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
@@ -47095,7 +47095,7 @@
       </c>
       <c r="O617" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="O618" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
@@ -47247,7 +47247,7 @@
       </c>
       <c r="O619" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="O620" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="O621" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="O622" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
@@ -47551,7 +47551,7 @@
       </c>
       <c r="O623" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="O624" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
@@ -47703,7 +47703,7 @@
       </c>
       <c r="O625" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 19:02:29</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="O626" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 19:02:29</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="O627" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
@@ -47931,7 +47931,7 @@
       </c>
       <c r="O628" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="O629" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="O630" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
@@ -48159,7 +48159,7 @@
       </c>
       <c r="O631" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
@@ -48463,7 +48463,7 @@
       </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
@@ -48767,7 +48767,7 @@
       </c>
       <c r="O639" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P639" s="4" t="inlineStr">
@@ -48843,7 +48843,7 @@
       </c>
       <c r="O640" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>19/08/2026 07:11:18</t>
         </is>
       </c>
       <c r="P640" s="4" t="inlineStr">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
@@ -49223,7 +49223,7 @@
       </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
@@ -49527,7 +49527,7 @@
       </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P650" s="4" t="inlineStr">
@@ -49755,7 +49755,7 @@
       </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P652" s="4" t="inlineStr">
@@ -49831,7 +49831,7 @@
       </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P653" s="4" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P654" s="4" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P655" s="4" t="inlineStr">
@@ -50059,7 +50059,7 @@
       </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P656" s="4" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P657" s="4" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P660" s="4" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P661" s="4" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P662" s="4" t="inlineStr">
@@ -50591,7 +50591,7 @@
       </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P663" s="4" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P664" s="4" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P665" s="4" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P666" s="4" t="inlineStr">
@@ -50895,7 +50895,7 @@
       </c>
       <c r="O667" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P667" s="4" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="O668" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P668" s="4" t="inlineStr">
@@ -51047,7 +51047,7 @@
       </c>
       <c r="O669" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P669" s="4" t="inlineStr">
@@ -51199,7 +51199,7 @@
       </c>
       <c r="O671" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P671" s="4" t="inlineStr">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="O672" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P672" s="4" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="O673" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P673" s="4" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="O674" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P674" s="4" t="inlineStr">
@@ -51503,7 +51503,7 @@
       </c>
       <c r="O675" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P675" s="4" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O677" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>18/08/2026 07:14:11</t>
         </is>
       </c>
       <c r="P677" s="4" t="inlineStr">
@@ -51731,7 +51731,7 @@
       </c>
       <c r="O678" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P678" s="4" t="inlineStr">
@@ -51807,7 +51807,7 @@
       </c>
       <c r="O679" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P679" s="4" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O680" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P680" s="4" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="O681" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P681" s="4" t="inlineStr">
@@ -52035,7 +52035,7 @@
       </c>
       <c r="O682" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P682" s="4" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O684" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P684" s="4" t="inlineStr">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="O685" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P685" s="4" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="O686" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P686" s="4" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="O687" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P687" s="4" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P689" s="4" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="O690" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P690" s="4" t="inlineStr">
@@ -52719,7 +52719,7 @@
       </c>
       <c r="O691" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P691" s="4" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="O694" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P694" s="4" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="O695" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P695" s="4" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="O696" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P696" s="4" t="inlineStr">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="O697" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P697" s="4" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="O699" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P699" s="4" t="inlineStr">
@@ -53403,7 +53403,7 @@
       </c>
       <c r="O700" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P700" s="4" t="inlineStr">
@@ -53479,7 +53479,7 @@
       </c>
       <c r="O701" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P701" s="4" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="O702" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P702" s="4" t="inlineStr">
@@ -53631,7 +53631,7 @@
       </c>
       <c r="O703" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P703" s="4" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O704" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P704" s="4" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="O705" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P705" s="4" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O706" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P706" s="4" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="O707" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P707" s="4" t="inlineStr">
@@ -54087,7 +54087,7 @@
       </c>
       <c r="O709" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P709" s="4" t="inlineStr">
@@ -54163,7 +54163,7 @@
       </c>
       <c r="O710" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P710" s="4" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="O711" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P711" s="4" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="O712" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P712" s="4" t="inlineStr">
@@ -54543,7 +54543,7 @@
       </c>
       <c r="O715" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P715" s="4" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="O716" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P716" s="4" t="inlineStr">
@@ -54695,7 +54695,7 @@
       </c>
       <c r="O717" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P717" s="4" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="O718" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P718" s="4" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="O719" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P719" s="4" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="O721" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P721" s="4" t="inlineStr">
@@ -55075,7 +55075,7 @@
       </c>
       <c r="O722" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>18/08/2026 07:02:11</t>
         </is>
       </c>
       <c r="P722" s="4" t="inlineStr">
@@ -55151,7 +55151,7 @@
       </c>
       <c r="O723" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>21/08/2026 07:01:06</t>
         </is>
       </c>
       <c r="P723" s="4" t="inlineStr">
@@ -55227,7 +55227,7 @@
       </c>
       <c r="O724" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P724" s="4" t="inlineStr">
@@ -55303,7 +55303,7 @@
       </c>
       <c r="O725" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P725" s="4" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="O726" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P726" s="4" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="O727" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P727" s="4" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="O728" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P728" s="4" t="inlineStr">
@@ -55607,7 +55607,7 @@
       </c>
       <c r="O729" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P729" s="4" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="O730" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P730" s="4" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="O731" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P731" s="4" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="O732" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P732" s="4" t="inlineStr">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="O733" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P733" s="4" t="inlineStr">
@@ -55987,7 +55987,7 @@
       </c>
       <c r="O734" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>19/08/2026 07:11:18</t>
         </is>
       </c>
       <c r="P734" s="4" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="O735" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P735" s="4" t="inlineStr">
@@ -56139,7 +56139,7 @@
       </c>
       <c r="O736" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P736" s="4" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="O737" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P737" s="4" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="O738" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P738" s="4" t="inlineStr">
@@ -56367,7 +56367,7 @@
       </c>
       <c r="O739" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P739" s="4" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="O740" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P740" s="4" t="inlineStr">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="O741" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:13:31</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P741" s="4" t="inlineStr">
@@ -56595,7 +56595,7 @@
       </c>
       <c r="O742" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P742" s="4" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="O743" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:07:44</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P743" s="4" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="O744" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:14:34</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P744" s="4" t="inlineStr">
@@ -56823,7 +56823,7 @@
       </c>
       <c r="O745" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>23/08/2026 07:12:11</t>
         </is>
       </c>
       <c r="P745" s="4" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="O746" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>21/08/2026 07:05:05</t>
         </is>
       </c>
       <c r="P746" s="4" t="inlineStr">
@@ -56975,7 +56975,7 @@
       </c>
       <c r="O747" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>18/08/2026 07:07:17</t>
         </is>
       </c>
       <c r="P747" s="4" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="O748" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:03:12</t>
+          <t>21/08/2026 07:02:07</t>
         </is>
       </c>
       <c r="P748" s="4" t="inlineStr">
@@ -57127,7 +57127,7 @@
       </c>
       <c r="O749" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>18/08/2026 07:10:11</t>
         </is>
       </c>
       <c r="P749" s="4" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="O750" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:14:07</t>
+          <t>23/08/2026 07:15:08</t>
         </is>
       </c>
       <c r="P750" s="4" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="O751" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:14:07</t>
+          <t>23/08/2026 07:15:08</t>
         </is>
       </c>
       <c r="P751" s="4" t="inlineStr">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="O752" s="4" t="inlineStr">
         <is>
-          <t>15/08/2026 07:14:07</t>
+          <t>23/08/2026 07:15:08</t>
         </is>
       </c>
       <c r="P752" s="4" t="inlineStr">
@@ -57431,7 +57431,7 @@
       </c>
       <c r="O753" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P753" s="4" t="inlineStr">
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O754" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P754" s="4" t="inlineStr">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O755" s="4" t="inlineStr">
         <is>
-          <t>29/07/2026 07:37:08</t>
+          <t>19/08/2026 07:10:04</t>
         </is>
       </c>
       <c r="P755" s="4" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="O756" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P756" s="4" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="O757" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P757" s="4" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="O758" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P758" s="4" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="O759" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P759" s="4" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="O760" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P760" s="4" t="inlineStr">
@@ -58039,7 +58039,7 @@
       </c>
       <c r="O761" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P761" s="4" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="O762" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P762" s="4" t="inlineStr">
@@ -58191,7 +58191,7 @@
       </c>
       <c r="O763" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P763" s="4" t="inlineStr">
@@ -58267,7 +58267,7 @@
       </c>
       <c r="O764" s="4" t="inlineStr">
         <is>
-          <t>08/08/2026 07:05:14</t>
+          <t>23/08/2026 07:11:33</t>
         </is>
       </c>
       <c r="P764" s="4" t="inlineStr">
@@ -58569,7 +58569,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
+++ b/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 19:03:10</t>
+          <t>30/08/2026 07:26:04</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>02/09/2026 13:46:04</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>02/09/2026 13:44:05</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>02/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:00:05</t>
+          <t>28/08/2026 07:00:05</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 18:42:50</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:06:03</t>
+          <t>28/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>27/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:06:03</t>
+          <t>28/08/2026 07:03:04</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>27/08/2026 07:09:04</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>02/09/2026 13:46:04</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:10:04</t>
+          <t>02/09/2026 13:44:05</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>02/09/2026 13:44:05</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>25/08/2026 07:07:22</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 18:53:13</t>
+          <t>25/08/2026 07:07:22</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:08:25</t>
+          <t>25/08/2026 07:07:22</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>02/09/2026 13:46:04</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>02/09/2026 13:44:05</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P222" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="O223" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P223" s="4" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P224" s="4" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="O225" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P225" s="4" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P226" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="O227" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P227" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P228" s="4" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P229" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P230" s="4" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="O231" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P231" s="4" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P232" s="4" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O233" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P233" s="4" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P234" s="4" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P235" s="4" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P236" s="4" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P237" s="4" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P238" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P239" s="4" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P240" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P241" s="4" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P242" s="4" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P243" s="4" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P244" s="4" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P245" s="4" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P246" s="4" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P247" s="4" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P248" s="4" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P249" s="4" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P250" s="4" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P251" s="4" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P252" s="4" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P253" s="4" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P254" s="4" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P255" s="4" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P257" s="4" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P258" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P259" s="4" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P260" s="4" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P261" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P262" s="4" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P265" s="4" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P266" s="4" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P267" s="4" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P269" s="4" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P270" s="4" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P271" s="4" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O272" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P272" s="4" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O273" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P273" s="4" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="O275" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P275" s="4" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O277" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P277" s="4" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O279" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P279" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P281" s="4" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P282" s="4" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P283" s="4" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P284" s="4" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P285" s="4" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P286" s="4" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P287" s="4" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P288" s="4" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P289" s="4" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P290" s="4" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P291" s="4" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P292" s="4" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P293" s="4" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P295" s="4" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P297" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P298" s="4" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P299" s="4" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P300" s="4" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P301" s="4" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P302" s="4" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P303" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P304" s="4" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P305" s="4" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P306" s="4" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P307" s="4" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P308" s="4" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P309" s="4" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P310" s="4" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P311" s="4" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P312" s="4" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P313" s="4" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P314" s="4" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P315" s="4" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P316" s="4" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P317" s="4" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P318" s="4" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P319" s="4" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P320" s="4" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P321" s="4" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P322" s="4" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P323" s="4" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P324" s="4" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P325" s="4" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P326" s="4" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P327" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P328" s="4" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P329" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P330" s="4" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P331" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P332" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P333" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P334" s="4" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P335" s="4" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P336" s="4" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P337" s="4" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P338" s="4" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P339" s="4" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P340" s="4" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P341" s="4" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P342" s="4" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>30/08/2026 07:29:06</t>
         </is>
       </c>
       <c r="P343" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>30/08/2026 07:29:06</t>
         </is>
       </c>
       <c r="P344" s="4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P345" s="4" t="inlineStr">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P346" s="4" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P348" s="4" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>30/08/2026 07:29:06</t>
         </is>
       </c>
       <c r="P349" s="4" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>01/09/2026 07:12:05</t>
         </is>
       </c>
       <c r="P350" s="4" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P351" s="4" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P352" s="4" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P353" s="4" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P354" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P355" s="4" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P356" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P357" s="4" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P358" s="4" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P359" s="4" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P360" s="4" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P361" s="4" t="inlineStr">
@@ -27715,7 +27715,7 @@
       </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P362" s="4" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P363" s="4" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P364" s="4" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P365" s="4" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P366" s="4" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P367" s="4" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P368" s="4" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P369" s="4" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P370" s="4" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P371" s="4" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P372" s="4" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P373" s="4" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P374" s="4" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P375" s="4" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P376" s="4" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P377" s="4" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P378" s="4" t="inlineStr">
@@ -29007,7 +29007,7 @@
       </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>01/09/2026 07:00:07</t>
         </is>
       </c>
       <c r="P379" s="4" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P380" s="4" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P381" s="4" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P382" s="4" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P383" s="4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P384" s="4" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P385" s="4" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P386" s="4" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P387" s="4" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P388" s="4" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P389" s="4" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P390" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P391" s="4" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P392" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P393" s="4" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P394" s="4" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P395" s="4" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P396" s="4" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P397" s="4" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="O398" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P398" s="4" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="O399" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P399" s="4" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="O400" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P400" s="4" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="O401" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P401" s="4" t="inlineStr">
@@ -30755,7 +30755,7 @@
       </c>
       <c r="O402" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P402" s="4" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P403" s="4" t="inlineStr">
@@ -30907,7 +30907,7 @@
       </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P404" s="4" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P405" s="4" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P406" s="4" t="inlineStr">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P407" s="4" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>27/08/2026 07:07:14</t>
         </is>
       </c>
       <c r="P408" s="4" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P409" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
       </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P410" s="4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P411" s="4" t="inlineStr">
@@ -31515,7 +31515,7 @@
       </c>
       <c r="O412" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P412" s="4" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="O413" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P413" s="4" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="O419" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:06:24</t>
+          <t>02/09/2026 07:06:04</t>
         </is>
       </c>
       <c r="P419" s="4" t="inlineStr">
@@ -32123,7 +32123,7 @@
       </c>
       <c r="O420" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:06:24</t>
+          <t>02/09/2026 07:06:04</t>
         </is>
       </c>
       <c r="P420" s="4" t="inlineStr">
@@ -32199,7 +32199,7 @@
       </c>
       <c r="O421" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:06:24</t>
+          <t>02/09/2026 07:06:04</t>
         </is>
       </c>
       <c r="P421" s="4" t="inlineStr">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="O422" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:06:24</t>
+          <t>02/09/2026 07:06:04</t>
         </is>
       </c>
       <c r="P422" s="4" t="inlineStr">
@@ -32351,7 +32351,7 @@
       </c>
       <c r="O423" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:06:24</t>
+          <t>02/09/2026 07:06:04</t>
         </is>
       </c>
       <c r="P423" s="4" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>30/08/2026 07:29:06</t>
         </is>
       </c>
       <c r="P427" s="4" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:06:05</t>
+          <t>30/08/2026 07:29:06</t>
         </is>
       </c>
       <c r="P428" s="4" t="inlineStr">
@@ -32807,7 +32807,7 @@
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P429" s="4" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P430" s="4" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P431" s="4" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P432" s="4" t="inlineStr">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P433" s="4" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P434" s="4" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P435" s="4" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P436" s="4" t="inlineStr">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P437" s="4" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P438" s="4" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P439" s="4" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P440" s="4" t="inlineStr">
@@ -33719,7 +33719,7 @@
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P441" s="4" t="inlineStr">
@@ -33795,7 +33795,7 @@
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P442" s="4" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P443" s="4" t="inlineStr">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P444" s="4" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P445" s="4" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P446" s="4" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P447" s="4" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P448" s="4" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P449" s="4" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P450" s="4" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P451" s="4" t="inlineStr">
@@ -34555,7 +34555,7 @@
       </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P452" s="4" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P453" s="4" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P454" s="4" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P455" s="4" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P456" s="4" t="inlineStr">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P457" s="4" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P458" s="4" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P459" s="4" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P460" s="4" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P461" s="4" t="inlineStr">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P462" s="4" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P463" s="4" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P464" s="4" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P465" s="4" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P466" s="4" t="inlineStr">
@@ -35695,7 +35695,7 @@
       </c>
       <c r="O467" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P467" s="4" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="O468" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P468" s="4" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P469" s="4" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P470" s="4" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P471" s="4" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P472" s="4" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P473" s="4" t="inlineStr">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P474" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P475" s="4" t="inlineStr">
@@ -36379,7 +36379,7 @@
       </c>
       <c r="O476" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>27/08/2026 07:00:11</t>
         </is>
       </c>
       <c r="P476" s="4" t="inlineStr">
@@ -36455,7 +36455,7 @@
       </c>
       <c r="O477" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:00:11</t>
+          <t>30/08/2026 07:16:20</t>
         </is>
       </c>
       <c r="P477" s="4" t="inlineStr">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="O480" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:13:04</t>
+          <t>01/09/2026 07:11:04</t>
         </is>
       </c>
       <c r="P480" s="4" t="inlineStr">
@@ -36759,7 +36759,7 @@
       </c>
       <c r="O481" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:13:04</t>
+          <t>01/09/2026 07:11:04</t>
         </is>
       </c>
       <c r="P481" s="4" t="inlineStr">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="O482" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026 19:04:05</t>
+          <t>31/08/2026 14:59:00</t>
         </is>
       </c>
       <c r="P482" s="4" t="inlineStr">
@@ -36911,7 +36911,7 @@
       </c>
       <c r="O483" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026 19:04:05</t>
+          <t>31/08/2026 15:13:47</t>
         </is>
       </c>
       <c r="P483" s="4" t="inlineStr">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="O484" s="4" t="inlineStr">
         <is>
-          <t>25/07/2026 07:08:11</t>
+          <t>01/09/2026 07:11:04</t>
         </is>
       </c>
       <c r="P484" s="4" t="inlineStr">
@@ -37063,7 +37063,7 @@
       </c>
       <c r="O485" s="4" t="inlineStr">
         <is>
-          <t>13/02/2026 11:54:59</t>
+          <t>31/08/2026 15:07:44</t>
         </is>
       </c>
       <c r="P485" s="4" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="O500" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 19:10:19</t>
+          <t>02/09/2026 07:15:04</t>
         </is>
       </c>
       <c r="P500" s="4" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P501" s="4" t="inlineStr">
@@ -38355,7 +38355,7 @@
       </c>
       <c r="O502" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P502" s="4" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O503" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P503" s="4" t="inlineStr">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="O504" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P504" s="4" t="inlineStr">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="O505" s="4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:03:27</t>
+          <t>02/09/2026 07:03:04</t>
         </is>
       </c>
       <c r="P505" s="4" t="inlineStr">
@@ -38659,7 +38659,7 @@
       </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P506" s="4" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P507" s="4" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P508" s="4" t="inlineStr">
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P509" s="4" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="O510" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P510" s="4" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P511" s="4" t="inlineStr">
@@ -39115,7 +39115,7 @@
       </c>
       <c r="O512" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P512" s="4" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="O513" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P513" s="4" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="O514" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P514" s="4" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="O515" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P515" s="4" t="inlineStr">
@@ -39419,7 +39419,7 @@
       </c>
       <c r="O516" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P516" s="4" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="O520" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>30/08/2026 07:19:04</t>
         </is>
       </c>
       <c r="P520" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>27/08/2026 07:05:04</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="O522" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>02/09/2026 13:43:04</t>
         </is>
       </c>
       <c r="P522" s="4" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="O523" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>02/09/2026 13:43:04</t>
         </is>
       </c>
       <c r="P523" s="4" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="O526" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>30/08/2026 07:19:04</t>
         </is>
       </c>
       <c r="P526" s="4" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="O530" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:03:04</t>
+          <t>30/08/2026 07:19:04</t>
         </is>
       </c>
       <c r="P530" s="4" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>02/09/2026 13:46:04</t>
         </is>
       </c>
       <c r="P536" s="4" t="inlineStr">
@@ -41015,7 +41015,7 @@
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P537" s="4" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P538" s="4" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P539" s="4" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P540" s="4" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>01/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P541" s="4" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>02/09/2026 13:46:04</t>
         </is>
       </c>
       <c r="P542" s="4" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:09:04</t>
+          <t>30/08/2026 07:31:06</t>
         </is>
       </c>
       <c r="P543" s="4" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>02/09/2026 13:41:06</t>
         </is>
       </c>
       <c r="P544" s="4" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P545" s="4" t="inlineStr">
@@ -41699,7 +41699,7 @@
       </c>
       <c r="O546" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P546" s="4" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>02/09/2026 13:44:05</t>
         </is>
       </c>
       <c r="P547" s="4" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>27/08/2026 07:02:12</t>
         </is>
       </c>
       <c r="P548" s="4" t="inlineStr">
@@ -41927,7 +41927,7 @@
       </c>
       <c r="O549" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>30/08/2026 07:17:15</t>
         </is>
       </c>
       <c r="P549" s="4" t="inlineStr">
@@ -42003,7 +42003,7 @@
       </c>
       <c r="O550" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P550" s="4" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>30/08/2026 07:21:17</t>
         </is>
       </c>
       <c r="P554" s="4" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P555" s="4" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:07:05</t>
+          <t>27/08/2026 07:10:06</t>
         </is>
       </c>
       <c r="P556" s="4" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P557" s="4" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P558" s="4" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="O559" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:05:14</t>
+          <t>01/09/2026 07:09:15</t>
         </is>
       </c>
       <c r="P559" s="4" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>27/08/2026 07:03:08</t>
         </is>
       </c>
       <c r="P560" s="4" t="inlineStr">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P561" s="4" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:01:14</t>
+          <t>01/09/2026 07:02:23</t>
         </is>
       </c>
       <c r="P562" s="4" t="inlineStr">
@@ -42991,7 +42991,7 @@
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
-          <t>20/08/2026 07:02:08</t>
+          <t>01/09/2026 07:04:12</t>
         </is>
       </c>
       <c r="P563" s="4" t="inlineStr">
@@ -43067,7 +43067,7 @@
       </c>
       <c r="O564" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:16:06</t>
+          <t>30/08/2026 07:28:04</t>
         </is>
       </c>
       <c r="P564" s="4" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="O565" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:16:06</t>
+          <t>30/08/2026 07:28:04</t>
         </is>
       </c>
       <c r="P565" s="4" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="O566" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:16:06</t>
+          <t>30/08/2026 07:28:04</t>
         </is>
       </c>
       <c r="P566" s="4" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="O567" s="4" t="inlineStr">
         <is>
-          <t>19/08/2026 07:11:18</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P567" s="4" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="O568" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P568" s="4" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="O569" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P569" s="4" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="O570" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P570" s="4" t="inlineStr">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="O571" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P571" s="4" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="O572" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P572" s="4" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O573" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P573" s="4" t="inlineStr">
@@ -43827,7 +43827,7 @@
       </c>
       <c r="O574" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P574" s="4" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P575" s="4" t="inlineStr">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="O576" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P576" s="4" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="O577" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P577" s="4" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="O578" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P578" s="4" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="O579" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P579" s="4" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O580" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P580" s="4" t="inlineStr">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="O581" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P581" s="4" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="O582" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P582" s="4" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="O583" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P583" s="4" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="O584" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P584" s="4" t="inlineStr">
@@ -44663,7 +44663,7 @@
       </c>
       <c r="O585" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P585" s="4" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="O586" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P586" s="4" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="O587" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P587" s="4" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
@@ -45271,7 +45271,7 @@
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
@@ -45423,7 +45423,7 @@
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="O600" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="O601" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P601" s="4" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="O602" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="O603" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O604" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O605" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O606" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="O607" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P607" s="4" t="inlineStr">
@@ -46411,7 +46411,7 @@
       </c>
       <c r="O608" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P608" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="O609" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="O610" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="O611" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="O612" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="O613" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="O614" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="O615" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P615" s="4" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O616" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
@@ -47095,7 +47095,7 @@
       </c>
       <c r="O617" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="O618" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
@@ -47247,7 +47247,7 @@
       </c>
       <c r="O619" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="O620" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="O621" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="O622" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
@@ -47551,7 +47551,7 @@
       </c>
       <c r="O623" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="O624" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
@@ -47703,7 +47703,7 @@
       </c>
       <c r="O625" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="O626" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="O627" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
@@ -47931,7 +47931,7 @@
       </c>
       <c r="O628" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="O629" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="O630" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
@@ -48159,7 +48159,7 @@
       </c>
       <c r="O631" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
@@ -48463,7 +48463,7 @@
       </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
@@ -48767,7 +48767,7 @@
       </c>
       <c r="O639" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P639" s="4" t="inlineStr">
@@ -48843,7 +48843,7 @@
       </c>
       <c r="O640" s="4" t="inlineStr">
         <is>
-          <t>19/08/2026 07:11:18</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P640" s="4" t="inlineStr">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
@@ -49223,7 +49223,7 @@
       </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
@@ -49527,7 +49527,7 @@
       </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P650" s="4" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="O651" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P651" s="4" t="inlineStr">
@@ -49755,7 +49755,7 @@
       </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P652" s="4" t="inlineStr">
@@ -49831,7 +49831,7 @@
       </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P653" s="4" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P654" s="4" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P655" s="4" t="inlineStr">
@@ -50059,7 +50059,7 @@
       </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P656" s="4" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P657" s="4" t="inlineStr">
@@ -50211,7 +50211,7 @@
       </c>
       <c r="O658" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:05:05</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P658" s="4" t="inlineStr">
@@ -50287,7 +50287,7 @@
       </c>
       <c r="O659" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P659" s="4" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P660" s="4" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P661" s="4" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P662" s="4" t="inlineStr">
@@ -50591,7 +50591,7 @@
       </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P663" s="4" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P664" s="4" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P665" s="4" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P666" s="4" t="inlineStr">
@@ -50895,7 +50895,7 @@
       </c>
       <c r="O667" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P667" s="4" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="O668" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P668" s="4" t="inlineStr">
@@ -51047,7 +51047,7 @@
       </c>
       <c r="O669" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P669" s="4" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="O670" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:40:34</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P670" s="4" t="inlineStr">
@@ -51199,7 +51199,7 @@
       </c>
       <c r="O671" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P671" s="4" t="inlineStr">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="O672" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P672" s="4" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="O673" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P673" s="4" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="O674" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P674" s="4" t="inlineStr">
@@ -51503,7 +51503,7 @@
       </c>
       <c r="O675" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P675" s="4" t="inlineStr">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="O676" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:09:12</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P676" s="4" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O677" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:14:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P677" s="4" t="inlineStr">
@@ -51731,7 +51731,7 @@
       </c>
       <c r="O678" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P678" s="4" t="inlineStr">
@@ -51807,7 +51807,7 @@
       </c>
       <c r="O679" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P679" s="4" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O680" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P680" s="4" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="O681" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P681" s="4" t="inlineStr">
@@ -52035,7 +52035,7 @@
       </c>
       <c r="O682" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P682" s="4" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O684" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P684" s="4" t="inlineStr">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="O685" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P685" s="4" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="O686" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P686" s="4" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="O687" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P687" s="4" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="O688" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P688" s="4" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P689" s="4" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="O690" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P690" s="4" t="inlineStr">
@@ -52719,7 +52719,7 @@
       </c>
       <c r="O691" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P691" s="4" t="inlineStr">
@@ -52795,7 +52795,7 @@
       </c>
       <c r="O692" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P692" s="4" t="inlineStr">
@@ -52871,7 +52871,7 @@
       </c>
       <c r="O693" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P693" s="4" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="O694" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P694" s="4" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="O695" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P695" s="4" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="O696" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P696" s="4" t="inlineStr">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="O697" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P697" s="4" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="O698" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P698" s="4" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="O699" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P699" s="4" t="inlineStr">
@@ -53403,7 +53403,7 @@
       </c>
       <c r="O700" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P700" s="4" t="inlineStr">
@@ -53479,7 +53479,7 @@
       </c>
       <c r="O701" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P701" s="4" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="O702" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P702" s="4" t="inlineStr">
@@ -53631,7 +53631,7 @@
       </c>
       <c r="O703" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P703" s="4" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O704" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P704" s="4" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="O705" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P705" s="4" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O706" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P706" s="4" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="O707" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P707" s="4" t="inlineStr">
@@ -54011,7 +54011,7 @@
       </c>
       <c r="O708" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P708" s="4" t="inlineStr">
@@ -54087,7 +54087,7 @@
       </c>
       <c r="O709" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P709" s="4" t="inlineStr">
@@ -54163,7 +54163,7 @@
       </c>
       <c r="O710" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P710" s="4" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="O711" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P711" s="4" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="O712" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P712" s="4" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="O713" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P713" s="4" t="inlineStr">
@@ -54467,7 +54467,7 @@
       </c>
       <c r="O714" s="4" t="inlineStr">
         <is>
-          <t>14/08/2026 07:01:05</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P714" s="4" t="inlineStr">
@@ -54543,7 +54543,7 @@
       </c>
       <c r="O715" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P715" s="4" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="O716" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P716" s="4" t="inlineStr">
@@ -54695,7 +54695,7 @@
       </c>
       <c r="O717" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P717" s="4" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="O718" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P718" s="4" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="O719" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P719" s="4" t="inlineStr">
@@ -54923,7 +54923,7 @@
       </c>
       <c r="O720" s="4" t="inlineStr">
         <is>
-          <t>13/08/2026 08:03:34</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P720" s="4" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="O721" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P721" s="4" t="inlineStr">
@@ -55075,7 +55075,7 @@
       </c>
       <c r="O722" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:02:11</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P722" s="4" t="inlineStr">
@@ -55151,7 +55151,7 @@
       </c>
       <c r="O723" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:01:06</t>
+          <t>02/09/2026 07:02:07</t>
         </is>
       </c>
       <c r="P723" s="4" t="inlineStr">
@@ -55227,7 +55227,7 @@
       </c>
       <c r="O724" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P724" s="4" t="inlineStr">
@@ -55303,7 +55303,7 @@
       </c>
       <c r="O725" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P725" s="4" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="O726" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P726" s="4" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="O727" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P727" s="4" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="O728" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P728" s="4" t="inlineStr">
@@ -55607,7 +55607,7 @@
       </c>
       <c r="O729" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P729" s="4" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="O730" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P730" s="4" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="O731" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P731" s="4" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="O732" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P732" s="4" t="inlineStr">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="O733" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P733" s="4" t="inlineStr">
@@ -55987,7 +55987,7 @@
       </c>
       <c r="O734" s="4" t="inlineStr">
         <is>
-          <t>19/08/2026 07:11:18</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P734" s="4" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="O735" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P735" s="4" t="inlineStr">
@@ -56139,7 +56139,7 @@
       </c>
       <c r="O736" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P736" s="4" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="O737" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P737" s="4" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="O738" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P738" s="4" t="inlineStr">
@@ -56367,7 +56367,7 @@
       </c>
       <c r="O739" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P739" s="4" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="O740" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P740" s="4" t="inlineStr">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="O741" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>30/08/2026 07:25:23</t>
         </is>
       </c>
       <c r="P741" s="4" t="inlineStr">
@@ -56595,7 +56595,7 @@
       </c>
       <c r="O742" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P742" s="4" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="O743" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P743" s="4" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="O744" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P744" s="4" t="inlineStr">
@@ -56823,7 +56823,7 @@
       </c>
       <c r="O745" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:12:11</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P745" s="4" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="O746" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:05:05</t>
+          <t>02/09/2026 07:12:08</t>
         </is>
       </c>
       <c r="P746" s="4" t="inlineStr">
@@ -56975,7 +56975,7 @@
       </c>
       <c r="O747" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:07:17</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P747" s="4" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="O748" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026 07:02:07</t>
+          <t>02/09/2026 07:05:10</t>
         </is>
       </c>
       <c r="P748" s="4" t="inlineStr">
@@ -57127,7 +57127,7 @@
       </c>
       <c r="O749" s="4" t="inlineStr">
         <is>
-          <t>18/08/2026 07:10:11</t>
+          <t>02/09/2026 07:08:07</t>
         </is>
       </c>
       <c r="P749" s="4" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="O750" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:15:08</t>
+          <t>30/08/2026 07:27:05</t>
         </is>
       </c>
       <c r="P750" s="4" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="O751" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:15:08</t>
+          <t>30/08/2026 07:27:05</t>
         </is>
       </c>
       <c r="P751" s="4" t="inlineStr">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="O752" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:15:08</t>
+          <t>30/08/2026 07:27:05</t>
         </is>
       </c>
       <c r="P752" s="4" t="inlineStr">
@@ -57431,7 +57431,7 @@
       </c>
       <c r="O753" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P753" s="4" t="inlineStr">
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O754" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P754" s="4" t="inlineStr">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O755" s="4" t="inlineStr">
         <is>
-          <t>19/08/2026 07:10:04</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P755" s="4" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="O756" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P756" s="4" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="O757" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P757" s="4" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="O758" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P758" s="4" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="O759" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P759" s="4" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="O760" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P760" s="4" t="inlineStr">
@@ -58039,7 +58039,7 @@
       </c>
       <c r="O761" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P761" s="4" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="O762" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P762" s="4" t="inlineStr">
@@ -58191,7 +58191,7 @@
       </c>
       <c r="O763" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P763" s="4" t="inlineStr">
@@ -58267,7 +58267,7 @@
       </c>
       <c r="O764" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026 07:11:33</t>
+          <t>02/09/2026 07:11:06</t>
         </is>
       </c>
       <c r="P764" s="4" t="inlineStr">
@@ -58569,7 +58569,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
+++ b/assets/data/ilo/catalog/catalogo_dataset_web_ove_oit_ilostat.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:46:04</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:44:05</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:00:07</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:00:05</t>
+          <t>08/09/2026 07:01:25</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>08/09/2026 07:00:31</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026 07:00:11</t>
+          <t>03/09/2026 14:52:05</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Remuneraciones y ingresos</t>
+          <t>Trabajadores en el sector público</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:03:04</t>
+          <t>08/09/2026 07:17:06</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Remuneraciones y ingresos</t>
+          <t>Trabajadores en el sector público</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:09:04</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Remuneraciones y ingresos</t>
+          <t>Trabajadores en el sector público</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026 07:03:04</t>
+          <t>08/09/2026 07:17:06</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Remuneraciones y ingresos</t>
+          <t>Trabajadores en el sector público</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:09:04</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 21:00:10</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:06:15</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:46:04</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:44:05</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:44:05</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026 07:07:22</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026 07:07:22</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026 07:07:22</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:46:04</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:44:05</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P222" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="O223" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P223" s="4" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P224" s="4" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="O225" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P225" s="4" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P226" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="O227" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:06:15</t>
         </is>
       </c>
       <c r="P227" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P228" s="4" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P229" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P230" s="4" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="O231" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P231" s="4" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P232" s="4" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O233" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P233" s="4" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P234" s="4" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P235" s="4" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P236" s="4" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P237" s="4" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P238" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P239" s="4" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P240" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P241" s="4" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P242" s="4" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P243" s="4" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P244" s="4" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P245" s="4" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P246" s="4" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P247" s="4" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P248" s="4" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P249" s="4" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P250" s="4" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P251" s="4" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P252" s="4" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P253" s="4" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P254" s="4" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 21:00:10</t>
         </is>
       </c>
       <c r="P255" s="4" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 21:00:10</t>
         </is>
       </c>
       <c r="P256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P257" s="4" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P258" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P259" s="4" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P260" s="4" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P261" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P262" s="4" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P265" s="4" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P266" s="4" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P267" s="4" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P269" s="4" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P270" s="4" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P271" s="4" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="O272" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P272" s="4" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O273" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P273" s="4" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="O275" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P275" s="4" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O277" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P277" s="4" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O279" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P279" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P281" s="4" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P282" s="4" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P283" s="4" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P284" s="4" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P285" s="4" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P286" s="4" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P287" s="4" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P288" s="4" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P289" s="4" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P290" s="4" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P291" s="4" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P292" s="4" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P293" s="4" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P295" s="4" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P297" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P298" s="4" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P299" s="4" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P300" s="4" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P301" s="4" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P302" s="4" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P303" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P304" s="4" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P305" s="4" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P306" s="4" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P307" s="4" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P308" s="4" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P309" s="4" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P310" s="4" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P311" s="4" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P312" s="4" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P313" s="4" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P314" s="4" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 21:00:10</t>
         </is>
       </c>
       <c r="P315" s="4" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 21:00:10</t>
         </is>
       </c>
       <c r="P316" s="4" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P317" s="4" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P318" s="4" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P319" s="4" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:18:13</t>
         </is>
       </c>
       <c r="P320" s="4" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P321" s="4" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P322" s="4" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P323" s="4" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P324" s="4" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P325" s="4" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P326" s="4" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P327" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P328" s="4" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P329" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P330" s="4" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P331" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P332" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P333" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P334" s="4" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P335" s="4" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P336" s="4" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P337" s="4" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P338" s="4" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P339" s="4" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P340" s="4" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P341" s="4" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P342" s="4" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:29:06</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P343" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:29:06</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P344" s="4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P345" s="4" t="inlineStr">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P346" s="4" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P348" s="4" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:29:06</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P349" s="4" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:12:05</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P350" s="4" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P351" s="4" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P352" s="4" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P353" s="4" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P354" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P355" s="4" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P356" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P357" s="4" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P358" s="4" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P359" s="4" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P360" s="4" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P361" s="4" t="inlineStr">
@@ -27715,7 +27715,7 @@
       </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P362" s="4" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P363" s="4" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P364" s="4" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 07:05:39</t>
         </is>
       </c>
       <c r="P365" s="4" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P366" s="4" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P367" s="4" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P368" s="4" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P369" s="4" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P370" s="4" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P371" s="4" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P372" s="4" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P373" s="4" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 07:05:39</t>
         </is>
       </c>
       <c r="P374" s="4" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>03/09/2026 07:02:19</t>
         </is>
       </c>
       <c r="P375" s="4" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 07:05:39</t>
         </is>
       </c>
       <c r="P376" s="4" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P377" s="4" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P378" s="4" t="inlineStr">
@@ -29007,7 +29007,7 @@
       </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:00:07</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P379" s="4" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P380" s="4" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P381" s="4" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P382" s="4" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P383" s="4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P384" s="4" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P385" s="4" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P386" s="4" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P387" s="4" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P388" s="4" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P389" s="4" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P390" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P391" s="4" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P392" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P393" s="4" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P394" s="4" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P396" s="4" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P397" s="4" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="O398" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P398" s="4" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="O399" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P399" s="4" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P405" s="4" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P406" s="4" t="inlineStr">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P407" s="4" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:07:14</t>
+          <t>03/09/2026 21:04:23</t>
         </is>
       </c>
       <c r="P408" s="4" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P409" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
       </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P410" s="4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P411" s="4" t="inlineStr">
@@ -31515,7 +31515,7 @@
       </c>
       <c r="O412" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P412" s="4" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="O413" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P413" s="4" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:29:06</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P427" s="4" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:29:06</t>
+          <t>09/09/2026 07:24:05</t>
         </is>
       </c>
       <c r="P428" s="4" t="inlineStr">
@@ -32807,7 +32807,7 @@
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P429" s="4" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P430" s="4" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P431" s="4" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P432" s="4" t="inlineStr">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P433" s="4" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P434" s="4" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P435" s="4" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P436" s="4" t="inlineStr">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P437" s="4" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P439" s="4" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P440" s="4" t="inlineStr">
@@ -33719,7 +33719,7 @@
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P441" s="4" t="inlineStr">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P444" s="4" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P445" s="4" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P446" s="4" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P447" s="4" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P449" s="4" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P450" s="4" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P451" s="4" t="inlineStr">
@@ -34555,7 +34555,7 @@
       </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P452" s="4" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P453" s="4" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P454" s="4" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P455" s="4" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P456" s="4" t="inlineStr">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P457" s="4" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P458" s="4" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P459" s="4" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P460" s="4" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P461" s="4" t="inlineStr">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>03/09/2026 07:00:13</t>
         </is>
       </c>
       <c r="P462" s="4" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P463" s="4" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P464" s="4" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P465" s="4" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P466" s="4" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P469" s="4" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P470" s="4" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P471" s="4" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P472" s="4" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P473" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P475" s="4" t="inlineStr">
@@ -36379,7 +36379,7 @@
       </c>
       <c r="O476" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:00:11</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P476" s="4" t="inlineStr">
@@ -36455,7 +36455,7 @@
       </c>
       <c r="O477" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:16:20</t>
+          <t>09/09/2026 07:00:15</t>
         </is>
       </c>
       <c r="P477" s="4" t="inlineStr">
@@ -37139,7 +37139,7 @@
       </c>
       <c r="O486" s="4" t="inlineStr">
         <is>
-          <t>19/05/2026 19:56:05</t>
+          <t>08/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P486" s="4" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P501" s="4" t="inlineStr">
@@ -38355,7 +38355,7 @@
       </c>
       <c r="O502" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P502" s="4" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O503" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P503" s="4" t="inlineStr">
@@ -38659,7 +38659,7 @@
       </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P506" s="4" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P507" s="4" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P508" s="4" t="inlineStr">
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P509" s="4" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="O510" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P510" s="4" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P511" s="4" t="inlineStr">
@@ -39115,7 +39115,7 @@
       </c>
       <c r="O512" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P512" s="4" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="O513" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P513" s="4" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="O514" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P514" s="4" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="O515" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P515" s="4" t="inlineStr">
@@ -39419,7 +39419,7 @@
       </c>
       <c r="O516" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P516" s="4" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="O520" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:19:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P520" s="4" t="inlineStr">
@@ -39755,7 +39755,7 @@
       </c>
       <c r="E521" s="4" t="inlineStr">
         <is>
-          <t>Indicador ODS 8.5.1: Ganancias por hora promedio de asalariados según sexo (moneda local)</t>
+          <t>Indicador ODS 8.5.1: Ganancias por hora promedio de asalariados según sexo y ocupación (moneda local)</t>
         </is>
       </c>
       <c r="F521" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:05:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="O522" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:43:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P522" s="4" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="O523" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:43:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P523" s="4" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="O526" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:19:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P526" s="4" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="O530" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:19:04</t>
+          <t>09/09/2026 07:16:04</t>
         </is>
       </c>
       <c r="P530" s="4" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:46:04</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P536" s="4" t="inlineStr">
@@ -41015,7 +41015,7 @@
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P537" s="4" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P538" s="4" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P539" s="4" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P540" s="4" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:14:07</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P541" s="4" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:46:04</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P542" s="4" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:31:06</t>
+          <t>09/09/2026 07:31:05</t>
         </is>
       </c>
       <c r="P543" s="4" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:41:06</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P544" s="4" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P545" s="4" t="inlineStr">
@@ -41699,7 +41699,7 @@
       </c>
       <c r="O546" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P546" s="4" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 13:44:05</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P547" s="4" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:02:12</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P548" s="4" t="inlineStr">
@@ -41927,7 +41927,7 @@
       </c>
       <c r="O549" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:17:15</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P549" s="4" t="inlineStr">
@@ -42003,7 +42003,7 @@
       </c>
       <c r="O550" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P550" s="4" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026 07:21:17</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P554" s="4" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P555" s="4" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:10:06</t>
+          <t>09/09/2026 07:25:07</t>
         </is>
       </c>
       <c r="P556" s="4" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P557" s="4" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P558" s="4" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="O559" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:09:15</t>
+          <t>09/09/2026 07:19:13</t>
         </is>
       </c>
       <c r="P559" s="4" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026 07:03:08</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P560" s="4" t="inlineStr">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P561" s="4" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:02:23</t>
+          <t>09/09/2026 07:07:15</t>
         </is>
       </c>
       <c r="P562" s="4" t="inlineStr">
@@ -42991,7 +42991,7 @@
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
-          <t>01/09/2026 07:04:12</t>
+          <t>09/09/2026 07:11:12</t>
         </is>
       </c>
       <c r="P563" s="4" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="O568" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P568" s="4" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="O569" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P569" s="4" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="O570" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P570" s="4" t="inlineStr">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="O571" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P571" s="4" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="O572" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P572" s="4" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O573" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P573" s="4" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P575" s="4" t="inlineStr">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="O576" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P576" s="4" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="O577" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P577" s="4" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="O578" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P578" s="4" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="O579" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P579" s="4" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O580" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P580" s="4" t="inlineStr">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="O581" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>03/09/2026 10:46:31</t>
         </is>
       </c>
       <c r="P581" s="4" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="O582" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P582" s="4" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="O583" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>03/09/2026 10:46:31</t>
         </is>
       </c>
       <c r="P583" s="4" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="O584" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>03/09/2026 10:46:31</t>
         </is>
       </c>
       <c r="P584" s="4" t="inlineStr">
@@ -44663,7 +44663,7 @@
       </c>
       <c r="O585" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>03/09/2026 10:46:31</t>
         </is>
       </c>
       <c r="P585" s="4" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="O586" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P586" s="4" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="O587" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:02:04</t>
         </is>
       </c>
       <c r="P587" s="4" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:02:04</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:02:04</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:02:04</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
@@ -45271,7 +45271,7 @@
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
@@ -45423,7 +45423,7 @@
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="O600" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="O601" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P601" s="4" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="O602" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="O603" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O604" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O605" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O606" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="O607" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P607" s="4" t="inlineStr">
@@ -46411,7 +46411,7 @@
       </c>
       <c r="O608" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P608" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="O609" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="O610" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="O611" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="O612" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="O613" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="O614" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="O615" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P615" s="4" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O616" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
@@ -47095,7 +47095,7 @@
       </c>
       <c r="O617" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="O618" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
@@ -47247,7 +47247,7 @@
       </c>
       <c r="O619" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="O620" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="O621" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="O622" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
@@ -47551,7 +47551,7 @@
       </c>
       <c r="O623" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="O624" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
@@ -47703,7 +47703,7 @@
       </c>
       <c r="O625" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="O626" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="O627" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
@@ -47931,7 +47931,7 @@
       </c>
       <c r="O628" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="O629" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="O630" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
@@ -48159,7 +48159,7 @@
       </c>
       <c r="O631" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
@@ -48463,7 +48463,7 @@
       </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
@@ -49223,7 +49223,7 @@
       </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
@@ -49527,7 +49527,7 @@
       </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P650" s="4" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="O651" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P651" s="4" t="inlineStr">
@@ -49755,7 +49755,7 @@
       </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P652" s="4" t="inlineStr">
@@ -49831,7 +49831,7 @@
       </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P653" s="4" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P654" s="4" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P655" s="4" t="inlineStr">
@@ -50059,7 +50059,7 @@
       </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P656" s="4" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P657" s="4" t="inlineStr">
@@ -50211,7 +50211,7 @@
       </c>
       <c r="O658" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P658" s="4" t="inlineStr">
@@ -50287,7 +50287,7 @@
       </c>
       <c r="O659" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P659" s="4" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P660" s="4" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P661" s="4" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P662" s="4" t="inlineStr">
@@ -50591,7 +50591,7 @@
       </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P663" s="4" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P664" s="4" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P665" s="4" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P666" s="4" t="inlineStr">
@@ -50895,7 +50895,7 @@
       </c>
       <c r="O667" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P667" s="4" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="O668" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P668" s="4" t="inlineStr">
@@ -51047,7 +51047,7 @@
       </c>
       <c r="O669" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P669" s="4" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="O670" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P670" s="4" t="inlineStr">
@@ -51199,7 +51199,7 @@
       </c>
       <c r="O671" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P671" s="4" t="inlineStr">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="O672" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P672" s="4" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="O673" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P673" s="4" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="O674" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P674" s="4" t="inlineStr">
@@ -51503,7 +51503,7 @@
       </c>
       <c r="O675" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P675" s="4" t="inlineStr">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="O676" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P676" s="4" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O677" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P677" s="4" t="inlineStr">
@@ -51731,7 +51731,7 @@
       </c>
       <c r="O678" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P678" s="4" t="inlineStr">
@@ -51807,7 +51807,7 @@
       </c>
       <c r="O679" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P679" s="4" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O680" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P680" s="4" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="O681" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P681" s="4" t="inlineStr">
@@ -52035,7 +52035,7 @@
       </c>
       <c r="O682" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P682" s="4" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O684" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P684" s="4" t="inlineStr">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="O685" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P685" s="4" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="O686" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P686" s="4" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="O687" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P687" s="4" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="O688" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P688" s="4" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P689" s="4" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="O690" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P690" s="4" t="inlineStr">
@@ -52719,7 +52719,7 @@
       </c>
       <c r="O691" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P691" s="4" t="inlineStr">
@@ -52795,7 +52795,7 @@
       </c>
       <c r="O692" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P692" s="4" t="inlineStr">
@@ -52871,7 +52871,7 @@
       </c>
       <c r="O693" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P693" s="4" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="O694" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P694" s="4" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="O695" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P695" s="4" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="O696" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P696" s="4" t="inlineStr">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="O697" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P697" s="4" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="O698" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P698" s="4" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="O699" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P699" s="4" t="inlineStr">
@@ -53403,7 +53403,7 @@
       </c>
       <c r="O700" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P700" s="4" t="inlineStr">
@@ -53479,7 +53479,7 @@
       </c>
       <c r="O701" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P701" s="4" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="O702" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P702" s="4" t="inlineStr">
@@ -53631,7 +53631,7 @@
       </c>
       <c r="O703" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P703" s="4" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O704" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P704" s="4" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="O705" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P705" s="4" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O706" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P706" s="4" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="O707" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P707" s="4" t="inlineStr">
@@ -54011,7 +54011,7 @@
       </c>
       <c r="O708" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P708" s="4" t="inlineStr">
@@ -54087,7 +54087,7 @@
       </c>
       <c r="O709" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P709" s="4" t="inlineStr">
@@ -54163,7 +54163,7 @@
       </c>
       <c r="O710" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P710" s="4" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="O711" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P711" s="4" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="O712" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P712" s="4" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="O713" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P713" s="4" t="inlineStr">
@@ -54467,7 +54467,7 @@
       </c>
       <c r="O714" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P714" s="4" t="inlineStr">
@@ -54543,7 +54543,7 @@
       </c>
       <c r="O715" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P715" s="4" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="O716" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P716" s="4" t="inlineStr">
@@ -54695,7 +54695,7 @@
       </c>
       <c r="O717" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P717" s="4" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="O718" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P718" s="4" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="O719" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P719" s="4" t="inlineStr">
@@ -54923,7 +54923,7 @@
       </c>
       <c r="O720" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P720" s="4" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="O721" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P721" s="4" t="inlineStr">
@@ -55075,7 +55075,7 @@
       </c>
       <c r="O722" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P722" s="4" t="inlineStr">
@@ -55151,7 +55151,7 @@
       </c>
       <c r="O723" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:02:07</t>
+          <t>09/09/2026 07:03:11</t>
         </is>
       </c>
       <c r="P723" s="4" t="inlineStr">
@@ -55227,7 +55227,7 @@
       </c>
       <c r="O724" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P724" s="4" t="inlineStr">
@@ -55303,7 +55303,7 @@
       </c>
       <c r="O725" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P725" s="4" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="O726" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P726" s="4" t="inlineStr">
@@ -55455,7 +55455,7 @@
       </c>
       <c r="O727" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P727" s="4" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="O728" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P728" s="4" t="inlineStr">
@@ -55607,7 +55607,7 @@
       </c>
       <c r="O729" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P729" s="4" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="O730" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P730" s="4" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="O731" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P731" s="4" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="O732" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P732" s="4" t="inlineStr">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="O733" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P733" s="4" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="O735" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P735" s="4" t="inlineStr">
@@ -56139,7 +56139,7 @@
       </c>
       <c r="O736" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P736" s="4" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="O737" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P737" s="4" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="O738" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P738" s="4" t="inlineStr">
@@ -56367,7 +56367,7 @@
       </c>
       <c r="O739" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P739" s="4" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="O740" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P740" s="4" t="inlineStr">
@@ -56595,7 +56595,7 @@
       </c>
       <c r="O742" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P742" s="4" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="O743" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P743" s="4" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="O744" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P744" s="4" t="inlineStr">
@@ -56823,7 +56823,7 @@
       </c>
       <c r="O745" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P745" s="4" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="O746" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:12:08</t>
+          <t>09/09/2026 07:22:11</t>
         </is>
       </c>
       <c r="P746" s="4" t="inlineStr">
@@ -56975,7 +56975,7 @@
       </c>
       <c r="O747" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P747" s="4" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="O748" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:05:10</t>
+          <t>09/09/2026 07:10:12</t>
         </is>
       </c>
       <c r="P748" s="4" t="inlineStr">
@@ -57127,7 +57127,7 @@
       </c>
       <c r="O749" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:08:07</t>
+          <t>09/09/2026 07:14:07</t>
         </is>
       </c>
       <c r="P749" s="4" t="inlineStr">
@@ -57431,7 +57431,7 @@
       </c>
       <c r="O753" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P753" s="4" t="inlineStr">
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O754" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P754" s="4" t="inlineStr">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O755" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P755" s="4" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="O756" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P756" s="4" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="O757" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P757" s="4" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="O758" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P758" s="4" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="O759" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P759" s="4" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="O760" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P760" s="4" t="inlineStr">
@@ -58039,7 +58039,7 @@
       </c>
       <c r="O761" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P761" s="4" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="O762" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P762" s="4" t="inlineStr">
@@ -58191,7 +58191,7 @@
       </c>
       <c r="O763" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P763" s="4" t="inlineStr">
@@ -58267,7 +58267,7 @@
       </c>
       <c r="O764" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026 07:11:06</t>
+          <t>09/09/2026 07:20:06</t>
         </is>
       </c>
       <c r="P764" s="4" t="inlineStr">
@@ -58569,7 +58569,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
